--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727352</v>
+        <v>127727389</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539002</v>
+        <v>538633</v>
       </c>
       <c r="R2" t="n">
-        <v>7244475</v>
+        <v>7244525</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +748,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727333</v>
+        <v>127727369</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539048</v>
+        <v>538906</v>
       </c>
       <c r="R3" t="n">
-        <v>7244482</v>
+        <v>7244545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,26 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>stående 2stammig lutar</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # stående 2stammig lutar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727369</v>
+        <v>127727333</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>92029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538906</v>
+        <v>539048</v>
       </c>
       <c r="R4" t="n">
-        <v>7244545</v>
+        <v>7244482</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,6 +975,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>stående 2stammig lutar</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # stående 2stammig lutar</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727389</v>
+        <v>127727352</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538633</v>
+        <v>539002</v>
       </c>
       <c r="R5" t="n">
-        <v>7244525</v>
+        <v>7244475</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,6 +1089,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1082,26 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727377</v>
+        <v>127727331</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>92029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539032</v>
+        <v>539188</v>
       </c>
       <c r="R6" t="n">
-        <v>7244470</v>
+        <v>7244462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727351</v>
+        <v>127727377</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>91328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,39 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539184</v>
+        <v>539032</v>
       </c>
       <c r="R7" t="n">
-        <v>7244459</v>
+        <v>7244470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,11 +1308,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1326,6 +1316,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Ny rotvälta</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Ny rotvälta</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1345,7 +1355,7 @@
         <v>127727385</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727341</v>
+        <v>127727394</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,39 +1480,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538761</v>
+        <v>539095</v>
       </c>
       <c r="R9" t="n">
-        <v>7244400</v>
+        <v>7244407</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,11 +1542,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1550,6 +1550,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1566,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727347</v>
+        <v>127727351</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539057</v>
+        <v>539184</v>
       </c>
       <c r="R10" t="n">
-        <v>7244431</v>
+        <v>7244459</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1673,45 +1693,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727331</v>
+        <v>127727347</v>
       </c>
       <c r="B11" t="n">
-        <v>92027</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539188</v>
+        <v>539057</v>
       </c>
       <c r="R11" t="n">
-        <v>7244462</v>
+        <v>7244431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,6 +1771,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1754,26 +1784,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1790,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727394</v>
+        <v>127727341</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539095</v>
+        <v>538761</v>
       </c>
       <c r="R12" t="n">
-        <v>7244407</v>
+        <v>7244400</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,6 +1878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1871,26 +1891,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727375</v>
+        <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539165</v>
+        <v>538600</v>
       </c>
       <c r="R13" t="n">
-        <v>7244399</v>
+        <v>7244556</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>Stående, död</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727378</v>
+        <v>127727375</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538857</v>
+        <v>539165</v>
       </c>
       <c r="R14" t="n">
-        <v>7244381</v>
+        <v>7244399</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,9 +2116,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2136,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727337</v>
+        <v>127727378</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>91328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,39 +2152,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538658</v>
+        <v>538857</v>
       </c>
       <c r="R15" t="n">
-        <v>7244502</v>
+        <v>7244381</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2214,11 +2214,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2227,6 +2222,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2246,7 +2256,7 @@
         <v>127727357</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727374</v>
+        <v>127727337</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,34 +2371,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538600</v>
+        <v>538658</v>
       </c>
       <c r="R17" t="n">
-        <v>7244556</v>
+        <v>7244502</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2423,6 +2438,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2431,26 +2451,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående, död</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2694,7 +2694,7 @@
         <v>127727363</v>
       </c>
       <c r="B20" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R21" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R22" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
         <v>127727360</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727399</v>
+        <v>127727383</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>91346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538900</v>
+        <v>538911</v>
       </c>
       <c r="R24" t="n">
-        <v>7244576</v>
+        <v>7244544</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3224,6 +3224,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3240,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727336</v>
+        <v>127727399</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,39 +3271,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538852</v>
+        <v>538900</v>
       </c>
       <c r="R25" t="n">
-        <v>7244404</v>
+        <v>7244576</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3316,11 +3331,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727383</v>
+        <v>127727336</v>
       </c>
       <c r="B26" t="n">
-        <v>91344</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3368,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538911</v>
+        <v>538852</v>
       </c>
       <c r="R26" t="n">
-        <v>7244544</v>
+        <v>7244404</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3420,6 +3435,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3428,26 +3448,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727346</v>
+        <v>127727353</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538953</v>
+        <v>538793</v>
       </c>
       <c r="R27" t="n">
-        <v>7244425</v>
+        <v>7244570</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727380</v>
+        <v>127727346</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,34 +3582,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538993</v>
+        <v>538953</v>
       </c>
       <c r="R28" t="n">
-        <v>7244440</v>
+        <v>7244425</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3644,6 +3649,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3652,21 +3662,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3683,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727395</v>
+        <v>127727380</v>
       </c>
       <c r="B29" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,21 +3689,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3721,7 +3716,7 @@
         <v>538993</v>
       </c>
       <c r="R29" t="n">
-        <v>7244472</v>
+        <v>7244440</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3775,14 +3770,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3800,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727353</v>
+        <v>127727395</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,39 +3801,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R30" t="n">
-        <v>7244570</v>
+        <v>7244472</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,11 +3863,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3871,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727393</v>
+        <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>91692</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538905</v>
+        <v>538633</v>
       </c>
       <c r="R31" t="n">
-        <v>7244572</v>
+        <v>7244525</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727386</v>
+        <v>127727393</v>
       </c>
       <c r="B32" t="n">
-        <v>91690</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538633</v>
+        <v>538905</v>
       </c>
       <c r="R32" t="n">
-        <v>7244525</v>
+        <v>7244572</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
         <v>127727372</v>
       </c>
       <c r="B33" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>127727358</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,10 +4365,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127727345</v>
+        <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,39 +4376,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>538931</v>
+        <v>538854</v>
       </c>
       <c r="R35" t="n">
-        <v>7244442</v>
+        <v>7244608</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4443,11 +4438,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4456,6 +4446,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Granlåga invid ån</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga invid ån</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4472,10 +4482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727388</v>
+        <v>127727359</v>
       </c>
       <c r="B36" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,34 +4493,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538854</v>
+        <v>538744</v>
       </c>
       <c r="R36" t="n">
-        <v>7244608</v>
+        <v>7244385</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4545,6 +4560,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4553,26 +4573,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granlåga invid ån</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga invid ån</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4589,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R37" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4699,7 +4699,7 @@
         <v>127727368</v>
       </c>
       <c r="B38" t="n">
-        <v>91699</v>
+        <v>91701</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4803,50 +4803,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727356</v>
+        <v>127727384</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>91742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>538874</v>
+        <v>539028</v>
       </c>
       <c r="R39" t="n">
-        <v>7244402</v>
+        <v>7244444</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4881,11 +4876,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4894,6 +4884,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4910,10 +4920,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727384</v>
+        <v>127727330</v>
       </c>
       <c r="B40" t="n">
-        <v>91740</v>
+        <v>91297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,21 +4931,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4945,10 +4955,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539028</v>
+        <v>538757</v>
       </c>
       <c r="R40" t="n">
-        <v>7244444</v>
+        <v>7244545</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5004,12 +5014,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5027,45 +5037,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>91295</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R41" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,6 +5115,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5108,26 +5128,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5147,7 +5147,7 @@
         <v>127727361</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727398</v>
+        <v>127727343</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,34 +5262,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538623</v>
+        <v>538886</v>
       </c>
       <c r="R43" t="n">
-        <v>7244488</v>
+        <v>7244392</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5322,6 +5327,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5348,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5388,10 +5398,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R44" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5455,10 +5465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727349</v>
+        <v>127727367</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>91628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,39 +5476,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539183</v>
+        <v>539047</v>
       </c>
       <c r="R45" t="n">
-        <v>7244439</v>
+        <v>7244483</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5533,11 +5538,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5546,6 +5546,16 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5562,10 +5572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727367</v>
+        <v>127727398</v>
       </c>
       <c r="B46" t="n">
-        <v>91626</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5573,21 +5583,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5597,10 +5607,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539047</v>
+        <v>538623</v>
       </c>
       <c r="R46" t="n">
-        <v>7244483</v>
+        <v>7244488</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5643,16 +5653,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5672,7 +5672,7 @@
         <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>127727335</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>127727344</v>
       </c>
       <c r="B50" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B51" t="n">
-        <v>57661</v>
+        <v>56846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,10 +6135,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6147,10 +6151,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R51" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6183,11 +6187,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6213,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B52" t="n">
-        <v>56844</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,16 +6224,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6242,14 +6241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R52" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6294,6 +6289,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6320,32 +6320,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727334</v>
+        <v>127727379</v>
       </c>
       <c r="B53" t="n">
-        <v>92027</v>
+        <v>91328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539146</v>
+        <v>538959</v>
       </c>
       <c r="R53" t="n">
-        <v>7244417</v>
+        <v>7244418</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727379</v>
+        <v>127727355</v>
       </c>
       <c r="B54" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6443,34 +6443,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538959</v>
+        <v>538621</v>
       </c>
       <c r="R54" t="n">
-        <v>7244418</v>
+        <v>7244491</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6505,6 +6510,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6513,21 +6523,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6544,10 +6539,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B55" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,7 +6570,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R55" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6624,7 +6619,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6651,50 +6646,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727334</v>
       </c>
       <c r="B56" t="n">
-        <v>57661</v>
+        <v>92029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>539146</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244417</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6729,11 +6719,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6742,6 +6727,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6761,7 +6761,7 @@
         <v>127727396</v>
       </c>
       <c r="B57" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727389</v>
+        <v>127727333</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>92029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538633</v>
+        <v>539048</v>
       </c>
       <c r="R2" t="n">
-        <v>7244525</v>
+        <v>7244482</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
+          <t>stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+          <t>Picea abies # stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727333</v>
+        <v>127727389</v>
       </c>
       <c r="B4" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539048</v>
+        <v>538633</v>
       </c>
       <c r="R4" t="n">
-        <v>7244482</v>
+        <v>7244525</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,12 +988,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>stående 2stammig lutar</t>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # stående 2stammig lutar</t>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727331</v>
+        <v>127727394</v>
       </c>
       <c r="B6" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539188</v>
+        <v>539095</v>
       </c>
       <c r="R6" t="n">
-        <v>7244462</v>
+        <v>7244407</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1469,32 +1469,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727394</v>
+        <v>127727331</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>92029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539095</v>
+        <v>539188</v>
       </c>
       <c r="R9" t="n">
-        <v>7244407</v>
+        <v>7244462</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727383</v>
+        <v>127727399</v>
       </c>
       <c r="B24" t="n">
-        <v>91346</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538911</v>
+        <v>538900</v>
       </c>
       <c r="R24" t="n">
-        <v>7244544</v>
+        <v>7244576</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3224,26 +3224,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3260,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727399</v>
+        <v>127727383</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>91346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,21 +3251,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538900</v>
+        <v>538911</v>
       </c>
       <c r="R25" t="n">
-        <v>7244576</v>
+        <v>7244544</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3341,6 +3321,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727353</v>
+        <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,39 +3475,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R27" t="n">
-        <v>7244570</v>
+        <v>7244440</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3542,11 +3537,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3555,6 +3545,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3571,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727346</v>
+        <v>127727395</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,39 +3587,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538953</v>
+        <v>538993</v>
       </c>
       <c r="R28" t="n">
-        <v>7244425</v>
+        <v>7244472</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,11 +3649,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3662,6 +3657,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3678,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727380</v>
+        <v>127727353</v>
       </c>
       <c r="B29" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,34 +3704,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R29" t="n">
-        <v>7244440</v>
+        <v>7244570</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3751,6 +3771,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3759,21 +3784,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3790,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727395</v>
+        <v>127727346</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,34 +3811,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538993</v>
+        <v>538953</v>
       </c>
       <c r="R30" t="n">
-        <v>7244472</v>
+        <v>7244425</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3863,6 +3878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3871,26 +3891,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727386</v>
+        <v>127727372</v>
       </c>
       <c r="B31" t="n">
-        <v>91692</v>
+        <v>91328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538633</v>
+        <v>538755</v>
       </c>
       <c r="R31" t="n">
-        <v>7244525</v>
+        <v>7244423</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granstubbe och låga</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granstubbe och låga</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727393</v>
+        <v>127727386</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>91692</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538905</v>
+        <v>538633</v>
       </c>
       <c r="R32" t="n">
-        <v>7244572</v>
+        <v>7244525</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727372</v>
+        <v>127727393</v>
       </c>
       <c r="B33" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,21 +4152,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538755</v>
+        <v>538905</v>
       </c>
       <c r="R33" t="n">
-        <v>7244423</v>
+        <v>7244572</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Granstubbe och låga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe och låga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127727388</v>
+        <v>127727345</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,34 +4376,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>538854</v>
+        <v>538931</v>
       </c>
       <c r="R35" t="n">
-        <v>7244608</v>
+        <v>7244442</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4438,6 +4443,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4446,26 +4456,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Granlåga invid ån</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga invid ån</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4482,10 +4472,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727359</v>
+        <v>127727388</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,39 +4483,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538744</v>
+        <v>538854</v>
       </c>
       <c r="R36" t="n">
-        <v>7244385</v>
+        <v>7244608</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4560,11 +4545,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4573,6 +4553,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Granlåga invid ån</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga invid ån</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4589,7 +4589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B37" t="n">
         <v>57663</v>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R37" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727343</v>
+        <v>127727398</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,39 +5262,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538886</v>
+        <v>538623</v>
       </c>
       <c r="R43" t="n">
-        <v>7244392</v>
+        <v>7244488</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5327,11 +5322,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5358,10 +5348,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727349</v>
+        <v>127727367</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,39 +5359,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539183</v>
+        <v>539047</v>
       </c>
       <c r="R44" t="n">
-        <v>7244439</v>
+        <v>7244483</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5436,11 +5421,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5449,6 +5429,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5465,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727367</v>
+        <v>127727343</v>
       </c>
       <c r="B45" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5476,34 +5466,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539047</v>
+        <v>538886</v>
       </c>
       <c r="R45" t="n">
-        <v>7244483</v>
+        <v>7244392</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5538,6 +5533,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5546,16 +5546,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5572,10 +5562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727398</v>
+        <v>127727349</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5583,34 +5573,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>538623</v>
+        <v>539183</v>
       </c>
       <c r="R46" t="n">
-        <v>7244488</v>
+        <v>7244439</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5643,6 +5638,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>88735</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,34 +5680,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R47" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,6 +5747,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5760,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>88735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R48" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5864,11 +5849,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,6 +5857,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B51" t="n">
-        <v>56846</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,14 +6135,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6151,10 +6147,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R51" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6187,6 +6183,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6213,10 +6214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>56846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6224,16 +6225,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6241,10 +6242,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R52" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6289,11 +6294,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6432,50 +6432,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727355</v>
+        <v>127727334</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>92029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538621</v>
+        <v>539146</v>
       </c>
       <c r="R54" t="n">
-        <v>7244491</v>
+        <v>7244417</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6510,11 +6505,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, rikligt</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6523,6 +6513,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6539,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727348</v>
+        <v>127727396</v>
       </c>
       <c r="B55" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6550,39 +6555,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539079</v>
+        <v>539008</v>
       </c>
       <c r="R55" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6617,11 +6617,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6630,6 +6625,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6646,45 +6661,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727334</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
-        <v>92029</v>
+        <v>57663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539146</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244417</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6719,6 +6739,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6727,21 +6752,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6758,10 +6768,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727396</v>
+        <v>127727348</v>
       </c>
       <c r="B57" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6769,34 +6779,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539008</v>
+        <v>539079</v>
       </c>
       <c r="R57" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6831,6 +6846,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6839,26 +6859,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727369</v>
+        <v>127727389</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538906</v>
+        <v>538633</v>
       </c>
       <c r="R3" t="n">
-        <v>7244545</v>
+        <v>7244525</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727389</v>
+        <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538633</v>
+        <v>539002</v>
       </c>
       <c r="R4" t="n">
-        <v>7244525</v>
+        <v>7244475</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,6 +987,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,26 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,27 +1016,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727352</v>
+        <v>127727369</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539002</v>
+        <v>538906</v>
       </c>
       <c r="R5" t="n">
-        <v>7244475</v>
+        <v>7244545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727399</v>
+        <v>127727336</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,34 +3154,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538900</v>
+        <v>538852</v>
       </c>
       <c r="R24" t="n">
-        <v>7244576</v>
+        <v>7244404</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3214,6 +3219,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3357,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727336</v>
+        <v>127727399</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,39 +3378,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538852</v>
+        <v>538900</v>
       </c>
       <c r="R26" t="n">
-        <v>7244404</v>
+        <v>7244576</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3433,11 +3438,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4365,10 +4365,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127727345</v>
+        <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,39 +4376,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>538931</v>
+        <v>538854</v>
       </c>
       <c r="R35" t="n">
-        <v>7244442</v>
+        <v>7244608</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4443,11 +4438,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4456,6 +4446,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Granlåga invid ån</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga invid ån</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4472,10 +4482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727388</v>
+        <v>127727359</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,34 +4493,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538854</v>
+        <v>538744</v>
       </c>
       <c r="R36" t="n">
-        <v>7244608</v>
+        <v>7244385</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4545,6 +4560,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4553,26 +4573,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granlåga invid ån</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga invid ån</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4589,7 +4589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B37" t="n">
         <v>57663</v>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R37" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4920,45 +4920,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B40" t="n">
-        <v>91297</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R40" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4993,6 +4998,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5001,26 +5011,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5037,50 +5027,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727356</v>
+        <v>127727330</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>91297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538874</v>
+        <v>538757</v>
       </c>
       <c r="R41" t="n">
-        <v>7244402</v>
+        <v>7244545</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5115,11 +5100,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,6 +5108,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>88735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,39 +5680,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R47" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5747,11 +5742,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5760,6 +5750,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5776,10 +5786,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>88735</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,34 +5797,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R48" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,6 +5864,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5857,26 +5877,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727394</v>
+        <v>127727377</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539095</v>
+        <v>539032</v>
       </c>
       <c r="R6" t="n">
-        <v>7244407</v>
+        <v>7244470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727377</v>
+        <v>127727331</v>
       </c>
       <c r="B7" t="n">
-        <v>91328</v>
+        <v>92029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539032</v>
+        <v>539188</v>
       </c>
       <c r="R7" t="n">
-        <v>7244470</v>
+        <v>7244462</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1469,32 +1469,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727331</v>
+        <v>127727394</v>
       </c>
       <c r="B9" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539188</v>
+        <v>539095</v>
       </c>
       <c r="R9" t="n">
-        <v>7244462</v>
+        <v>7244407</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727351</v>
+        <v>127727341</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539184</v>
+        <v>538761</v>
       </c>
       <c r="R10" t="n">
-        <v>7244459</v>
+        <v>7244400</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727347</v>
+        <v>127727351</v>
       </c>
       <c r="B11" t="n">
         <v>57663</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539057</v>
+        <v>539184</v>
       </c>
       <c r="R11" t="n">
-        <v>7244431</v>
+        <v>7244459</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727341</v>
+        <v>127727347</v>
       </c>
       <c r="B12" t="n">
         <v>57663</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538761</v>
+        <v>539057</v>
       </c>
       <c r="R12" t="n">
-        <v>7244400</v>
+        <v>7244431</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727375</v>
+        <v>127727378</v>
       </c>
       <c r="B14" t="n">
         <v>91328</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539165</v>
+        <v>538857</v>
       </c>
       <c r="R14" t="n">
-        <v>7244399</v>
+        <v>7244381</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,14 +2116,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2141,7 +2136,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727378</v>
+        <v>127727375</v>
       </c>
       <c r="B15" t="n">
         <v>91328</v>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538857</v>
+        <v>539165</v>
       </c>
       <c r="R15" t="n">
-        <v>7244381</v>
+        <v>7244399</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,9 +2228,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B21" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R21" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R22" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727380</v>
+        <v>127727346</v>
       </c>
       <c r="B27" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,34 +3475,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538993</v>
+        <v>538953</v>
       </c>
       <c r="R27" t="n">
-        <v>7244440</v>
+        <v>7244425</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3542,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3545,21 +3555,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3576,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727395</v>
+        <v>127727353</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,34 +3582,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R28" t="n">
-        <v>7244472</v>
+        <v>7244570</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,6 +3649,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3657,26 +3662,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3693,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727353</v>
+        <v>127727380</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,39 +3689,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R29" t="n">
-        <v>7244570</v>
+        <v>7244440</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3771,11 +3751,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3784,6 +3759,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3800,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727346</v>
+        <v>127727395</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,39 +3801,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538953</v>
+        <v>538993</v>
       </c>
       <c r="R30" t="n">
-        <v>7244425</v>
+        <v>7244472</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,11 +3863,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3871,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727372</v>
+        <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91328</v>
+        <v>91692</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538755</v>
+        <v>538633</v>
       </c>
       <c r="R31" t="n">
-        <v>7244423</v>
+        <v>7244525</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Granstubbe och låga</t>
+          <t>Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe och låga</t>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727386</v>
+        <v>127727393</v>
       </c>
       <c r="B32" t="n">
-        <v>91692</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538633</v>
+        <v>538905</v>
       </c>
       <c r="R32" t="n">
-        <v>7244525</v>
+        <v>7244572</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727393</v>
+        <v>127727372</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>91328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,21 +4152,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538905</v>
+        <v>538755</v>
       </c>
       <c r="R33" t="n">
-        <v>7244572</v>
+        <v>7244423</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Granstubbe och låga</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Granstubbe och låga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B36" t="n">
         <v>57663</v>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R36" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B37" t="n">
         <v>57663</v>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R37" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4803,45 +4803,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727384</v>
+        <v>127727356</v>
       </c>
       <c r="B39" t="n">
-        <v>91742</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539028</v>
+        <v>538874</v>
       </c>
       <c r="R39" t="n">
-        <v>7244444</v>
+        <v>7244402</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,6 +4881,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4884,26 +4894,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4920,50 +4910,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727356</v>
+        <v>127727384</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>91742</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538874</v>
+        <v>539028</v>
       </c>
       <c r="R40" t="n">
-        <v>7244402</v>
+        <v>7244444</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4998,11 +4983,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5011,6 +4991,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>91628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R43" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5332,6 +5332,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5348,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727367</v>
+        <v>127727398</v>
       </c>
       <c r="B44" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5359,21 +5369,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5383,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539047</v>
+        <v>538623</v>
       </c>
       <c r="R44" t="n">
-        <v>7244483</v>
+        <v>7244488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,16 +5439,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5455,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B45" t="n">
         <v>57663</v>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R45" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727349</v>
+        <v>127727343</v>
       </c>
       <c r="B46" t="n">
         <v>57663</v>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539183</v>
+        <v>538886</v>
       </c>
       <c r="R46" t="n">
-        <v>7244439</v>
+        <v>7244392</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B49" t="n">
         <v>57663</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R49" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,7 +6000,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B50" t="n">
         <v>57663</v>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R50" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6661,7 +6661,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B56" t="n">
         <v>57663</v>
@@ -6692,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R56" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,7 +6768,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B57" t="n">
         <v>57663</v>
@@ -6799,7 +6799,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R57" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727333</v>
       </c>
       <c r="B2" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127727389</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127727377</v>
       </c>
       <c r="B6" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727331</v>
+        <v>127727394</v>
       </c>
       <c r="B7" t="n">
-        <v>92029</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539188</v>
+        <v>539095</v>
       </c>
       <c r="R7" t="n">
-        <v>7244462</v>
+        <v>7244407</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727385</v>
+        <v>127727351</v>
       </c>
       <c r="B8" t="n">
-        <v>91346</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,34 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539028</v>
+        <v>539184</v>
       </c>
       <c r="R8" t="n">
-        <v>7244444</v>
+        <v>7244459</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1425,6 +1430,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1433,26 +1443,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727394</v>
+        <v>127727341</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,34 +1470,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539095</v>
+        <v>538761</v>
       </c>
       <c r="R9" t="n">
-        <v>7244407</v>
+        <v>7244400</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,6 +1537,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1550,26 +1550,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1586,50 +1566,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727341</v>
+        <v>127727331</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>92035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538761</v>
+        <v>539188</v>
       </c>
       <c r="R10" t="n">
-        <v>7244400</v>
+        <v>7244462</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,11 +1639,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1677,6 +1647,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727351</v>
+        <v>127727385</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>91352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,39 +1694,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539184</v>
+        <v>539028</v>
       </c>
       <c r="R11" t="n">
-        <v>7244459</v>
+        <v>7244444</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,11 +1756,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1784,6 +1764,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1910,7 +1910,7 @@
         <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>127727378</v>
       </c>
       <c r="B14" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>127727375</v>
       </c>
       <c r="B15" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>91334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R21" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B22" t="n">
-        <v>91328</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R22" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727336</v>
+        <v>127727383</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,39 +3154,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538852</v>
+        <v>538911</v>
       </c>
       <c r="R24" t="n">
-        <v>7244404</v>
+        <v>7244544</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3221,11 +3216,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3234,6 +3224,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3250,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727383</v>
+        <v>127727399</v>
       </c>
       <c r="B25" t="n">
-        <v>91346</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,21 +3271,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538911</v>
+        <v>538900</v>
       </c>
       <c r="R25" t="n">
-        <v>7244544</v>
+        <v>7244576</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,26 +3341,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3367,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727399</v>
+        <v>127727336</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,34 +3368,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538900</v>
+        <v>538852</v>
       </c>
       <c r="R26" t="n">
-        <v>7244576</v>
+        <v>7244404</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3438,6 +3433,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,7 +3464,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727346</v>
+        <v>127727353</v>
       </c>
       <c r="B27" t="n">
         <v>57663</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538953</v>
+        <v>538793</v>
       </c>
       <c r="R27" t="n">
-        <v>7244425</v>
+        <v>7244570</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727353</v>
+        <v>127727380</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>91334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,39 +3582,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R28" t="n">
-        <v>7244570</v>
+        <v>7244440</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,11 +3644,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3662,6 +3652,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3678,10 +3683,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727380</v>
+        <v>127727395</v>
       </c>
       <c r="B29" t="n">
-        <v>91328</v>
+        <v>91356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,21 +3694,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3716,7 +3721,7 @@
         <v>538993</v>
       </c>
       <c r="R29" t="n">
-        <v>7244440</v>
+        <v>7244472</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3770,9 +3775,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3790,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727395</v>
+        <v>127727346</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,34 +3811,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538993</v>
+        <v>538953</v>
       </c>
       <c r="R30" t="n">
-        <v>7244472</v>
+        <v>7244425</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3863,6 +3878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3871,26 +3891,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727386</v>
+        <v>127727393</v>
       </c>
       <c r="B31" t="n">
-        <v>91692</v>
+        <v>91356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538633</v>
+        <v>538905</v>
       </c>
       <c r="R31" t="n">
-        <v>7244525</v>
+        <v>7244572</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727393</v>
+        <v>127727358</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,34 +4035,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538905</v>
+        <v>538729</v>
       </c>
       <c r="R32" t="n">
-        <v>7244572</v>
+        <v>7244550</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4097,6 +4102,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4105,26 +4115,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4144,7 +4134,7 @@
         <v>127727372</v>
       </c>
       <c r="B33" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4258,50 +4248,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727358</v>
+        <v>127727386</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>91698</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538729</v>
+        <v>538633</v>
       </c>
       <c r="R34" t="n">
-        <v>7244550</v>
+        <v>7244525</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,11 +4321,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4349,6 +4329,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Grantickeporing på minst 4 grantickor</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>127727368</v>
       </c>
       <c r="B38" t="n">
-        <v>91701</v>
+        <v>91707</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4803,50 +4803,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727356</v>
+        <v>127727330</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>91303</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>538874</v>
+        <v>538757</v>
       </c>
       <c r="R39" t="n">
-        <v>7244402</v>
+        <v>7244545</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4881,11 +4876,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4894,6 +4884,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4913,7 +4923,7 @@
         <v>127727384</v>
       </c>
       <c r="B40" t="n">
-        <v>91742</v>
+        <v>91748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5027,45 +5037,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>91297</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R41" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,6 +5115,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5108,26 +5128,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727367</v>
+        <v>127727349</v>
       </c>
       <c r="B43" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,34 +5262,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539047</v>
+        <v>539183</v>
       </c>
       <c r="R43" t="n">
-        <v>7244483</v>
+        <v>7244439</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5329,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,16 +5342,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>91634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R44" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5439,6 +5439,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5455,10 +5465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727349</v>
+        <v>127727398</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,39 +5476,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539183</v>
+        <v>538623</v>
       </c>
       <c r="R45" t="n">
-        <v>7244439</v>
+        <v>7244488</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5531,11 +5536,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>88735</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,34 +5680,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R47" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,6 +5747,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5760,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>88741</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R48" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5864,11 +5849,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,6 +5857,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6320,32 +6320,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727379</v>
+        <v>127727334</v>
       </c>
       <c r="B53" t="n">
-        <v>91328</v>
+        <v>92035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>538959</v>
+        <v>539146</v>
       </c>
       <c r="R53" t="n">
-        <v>7244418</v>
+        <v>7244417</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,32 +6432,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727334</v>
+        <v>127727379</v>
       </c>
       <c r="B54" t="n">
-        <v>92029</v>
+        <v>91334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539146</v>
+        <v>538959</v>
       </c>
       <c r="R54" t="n">
-        <v>7244417</v>
+        <v>7244418</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6547,7 +6547,7 @@
         <v>127727396</v>
       </c>
       <c r="B55" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
         <v>57663</v>
@@ -6692,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,7 +6768,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B57" t="n">
         <v>57663</v>
@@ -6799,7 +6799,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R57" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727333</v>
+        <v>127727389</v>
       </c>
       <c r="B2" t="n">
-        <v>92035</v>
+        <v>91359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539048</v>
+        <v>538633</v>
       </c>
       <c r="R2" t="n">
-        <v>7244482</v>
+        <v>7244525</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>stående 2stammig lutar</t>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # stående 2stammig lutar</t>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,45 +792,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727389</v>
+        <v>127727369</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538633</v>
+        <v>538906</v>
       </c>
       <c r="R3" t="n">
-        <v>7244525</v>
+        <v>7244545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,26 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727352</v>
+        <v>127727333</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>92038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539002</v>
+        <v>539048</v>
       </c>
       <c r="R4" t="n">
-        <v>7244475</v>
+        <v>7244482</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +967,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,6 +975,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>stående 2stammig lutar</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # stående 2stammig lutar</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727369</v>
+        <v>127727352</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,7 +1042,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538906</v>
+        <v>539002</v>
       </c>
       <c r="R5" t="n">
-        <v>7244545</v>
+        <v>7244475</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,6 +1087,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727377</v>
+        <v>127727394</v>
       </c>
       <c r="B6" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539032</v>
+        <v>539095</v>
       </c>
       <c r="R6" t="n">
-        <v>7244470</v>
+        <v>7244407</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727394</v>
+        <v>127727351</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,34 +1246,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539095</v>
+        <v>539184</v>
       </c>
       <c r="R7" t="n">
-        <v>7244407</v>
+        <v>7244459</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,6 +1313,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1316,26 +1326,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727351</v>
+        <v>127727341</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539184</v>
+        <v>538761</v>
       </c>
       <c r="R8" t="n">
-        <v>7244459</v>
+        <v>7244400</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727341</v>
+        <v>127727377</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,39 +1460,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538761</v>
+        <v>539032</v>
       </c>
       <c r="R9" t="n">
-        <v>7244400</v>
+        <v>7244470</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,11 +1522,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1550,6 +1530,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Ny rotvälta</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Ny rotvälta</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1566,32 +1566,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727331</v>
+        <v>127727385</v>
       </c>
       <c r="B10" t="n">
-        <v>92035</v>
+        <v>91355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539188</v>
+        <v>539028</v>
       </c>
       <c r="R10" t="n">
-        <v>7244462</v>
+        <v>7244444</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727385</v>
+        <v>127727331</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>92038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539028</v>
+        <v>539188</v>
       </c>
       <c r="R11" t="n">
-        <v>7244444</v>
+        <v>7244462</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>127727347</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727374</v>
+        <v>127727357</v>
       </c>
       <c r="B13" t="n">
-        <v>91334</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538600</v>
+        <v>539013</v>
       </c>
       <c r="R13" t="n">
-        <v>7244556</v>
+        <v>7244500</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,6 +1985,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1988,26 +1998,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående, död</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727378</v>
+        <v>127727374</v>
       </c>
       <c r="B14" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538857</v>
+        <v>538600</v>
       </c>
       <c r="R14" t="n">
-        <v>7244381</v>
+        <v>7244556</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,9 +2106,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2139,7 +2134,7 @@
         <v>127727375</v>
       </c>
       <c r="B15" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727357</v>
+        <v>127727378</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,39 +2259,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539013</v>
+        <v>538857</v>
       </c>
       <c r="R16" t="n">
-        <v>7244500</v>
+        <v>7244381</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2331,11 +2321,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,6 +2329,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2363,7 +2363,7 @@
         <v>127727337</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>127727363</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127727387</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127727360</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>127727383</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>127727399</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>127727336</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727353</v>
+        <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,39 +3475,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R27" t="n">
-        <v>7244570</v>
+        <v>7244440</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3542,11 +3537,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3555,6 +3545,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3571,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727380</v>
+        <v>127727395</v>
       </c>
       <c r="B28" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,21 +3587,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3609,7 +3614,7 @@
         <v>538993</v>
       </c>
       <c r="R28" t="n">
-        <v>7244440</v>
+        <v>7244472</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3663,9 +3668,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3683,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727395</v>
+        <v>127727353</v>
       </c>
       <c r="B29" t="n">
-        <v>91356</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,34 +3704,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R29" t="n">
-        <v>7244472</v>
+        <v>7244570</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3756,6 +3771,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3764,26 +3784,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>127727346</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727393</v>
+        <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91356</v>
+        <v>91701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538905</v>
+        <v>538633</v>
       </c>
       <c r="R31" t="n">
-        <v>7244572</v>
+        <v>7244525</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727358</v>
+        <v>127727372</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,39 +4035,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538729</v>
+        <v>538755</v>
       </c>
       <c r="R32" t="n">
-        <v>7244550</v>
+        <v>7244423</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4102,11 +4097,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4115,6 +4105,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Granstubbe och låga</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe och låga</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4131,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727372</v>
+        <v>127727393</v>
       </c>
       <c r="B33" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,21 +4152,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4166,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538755</v>
+        <v>538905</v>
       </c>
       <c r="R33" t="n">
-        <v>7244423</v>
+        <v>7244572</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4225,12 +4235,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Granstubbe och låga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe och låga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4248,45 +4258,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727386</v>
+        <v>127727358</v>
       </c>
       <c r="B34" t="n">
-        <v>91698</v>
+        <v>57666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538633</v>
+        <v>538729</v>
       </c>
       <c r="R34" t="n">
-        <v>7244525</v>
+        <v>7244550</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,6 +4336,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4329,26 +4349,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R36" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R37" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4699,7 +4699,7 @@
         <v>127727368</v>
       </c>
       <c r="B38" t="n">
-        <v>91707</v>
+        <v>91710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>127727330</v>
       </c>
       <c r="B39" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>127727384</v>
       </c>
       <c r="B40" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>127727361</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>127727349</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727367</v>
+        <v>127727343</v>
       </c>
       <c r="B44" t="n">
-        <v>91634</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,34 +5369,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539047</v>
+        <v>538886</v>
       </c>
       <c r="R44" t="n">
-        <v>7244483</v>
+        <v>7244392</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5431,6 +5436,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5439,16 +5449,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5465,10 +5465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>91637</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R45" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5546,6 +5546,16 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5562,10 +5572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727343</v>
+        <v>127727398</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5573,39 +5583,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>538886</v>
+        <v>538623</v>
       </c>
       <c r="R46" t="n">
-        <v>7244392</v>
+        <v>7244488</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5638,11 +5643,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5672,7 +5672,7 @@
         <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R49" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,10 +6000,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B50" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R50" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,7 +6110,7 @@
         <v>127727339</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>127727371</v>
       </c>
       <c r="B52" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,32 +6320,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727334</v>
+        <v>127727379</v>
       </c>
       <c r="B53" t="n">
-        <v>92035</v>
+        <v>91337</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539146</v>
+        <v>538959</v>
       </c>
       <c r="R53" t="n">
-        <v>7244417</v>
+        <v>7244418</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727379</v>
+        <v>127727396</v>
       </c>
       <c r="B54" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6443,21 +6443,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538959</v>
+        <v>539008</v>
       </c>
       <c r="R54" t="n">
-        <v>7244418</v>
+        <v>7244491</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6524,9 +6524,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6544,32 +6549,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727396</v>
+        <v>127727334</v>
       </c>
       <c r="B55" t="n">
-        <v>91356</v>
+        <v>92038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539008</v>
+        <v>539146</v>
       </c>
       <c r="R55" t="n">
-        <v>7244491</v>
+        <v>7244417</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6636,14 +6641,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6664,7 +6664,7 @@
         <v>127727355</v>
       </c>
       <c r="B56" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>127727348</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727389</v>
+        <v>127727333</v>
       </c>
       <c r="B2" t="n">
-        <v>91359</v>
+        <v>92046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538633</v>
+        <v>539048</v>
       </c>
       <c r="R2" t="n">
-        <v>7244525</v>
+        <v>7244482</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
+          <t>stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+          <t>Picea abies # stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727369</v>
+        <v>127727389</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>91367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538906</v>
+        <v>538633</v>
       </c>
       <c r="R3" t="n">
-        <v>7244545</v>
+        <v>7244525</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,45 +909,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727333</v>
+        <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>92038</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539048</v>
+        <v>539002</v>
       </c>
       <c r="R4" t="n">
-        <v>7244482</v>
+        <v>7244475</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,6 +987,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,26 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>stående 2stammig lutar</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # stående 2stammig lutar</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,27 +1016,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727352</v>
+        <v>127727369</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539002</v>
+        <v>538906</v>
       </c>
       <c r="R5" t="n">
-        <v>7244475</v>
+        <v>7244545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727394</v>
+        <v>127727385</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539095</v>
+        <v>539028</v>
       </c>
       <c r="R6" t="n">
-        <v>7244407</v>
+        <v>7244444</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727351</v>
+        <v>127727394</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,39 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539184</v>
+        <v>539095</v>
       </c>
       <c r="R7" t="n">
-        <v>7244459</v>
+        <v>7244407</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,11 +1308,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1326,6 +1316,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1342,50 +1352,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727341</v>
+        <v>127727331</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>92046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538761</v>
+        <v>539188</v>
       </c>
       <c r="R8" t="n">
-        <v>7244400</v>
+        <v>7244462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,11 +1425,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1433,6 +1433,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1452,7 +1472,7 @@
         <v>127727377</v>
       </c>
       <c r="B9" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727385</v>
+        <v>127727341</v>
       </c>
       <c r="B10" t="n">
-        <v>91355</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539028</v>
+        <v>538761</v>
       </c>
       <c r="R10" t="n">
-        <v>7244444</v>
+        <v>7244400</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,6 +1664,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1647,26 +1677,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1683,45 +1693,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727331</v>
+        <v>127727351</v>
       </c>
       <c r="B11" t="n">
-        <v>92038</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539188</v>
+        <v>539184</v>
       </c>
       <c r="R11" t="n">
-        <v>7244462</v>
+        <v>7244459</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,6 +1771,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1764,26 +1784,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1803,7 +1803,7 @@
         <v>127727347</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727357</v>
+        <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539013</v>
+        <v>538600</v>
       </c>
       <c r="R13" t="n">
-        <v>7244500</v>
+        <v>7244556</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,11 +1980,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,6 +1988,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående, död</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2014,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727374</v>
+        <v>127727378</v>
       </c>
       <c r="B14" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538600</v>
+        <v>538857</v>
       </c>
       <c r="R14" t="n">
-        <v>7244556</v>
+        <v>7244381</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,14 +2116,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2134,7 +2139,7 @@
         <v>127727375</v>
       </c>
       <c r="B15" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727378</v>
+        <v>127727357</v>
       </c>
       <c r="B16" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,34 +2264,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538857</v>
+        <v>539013</v>
       </c>
       <c r="R16" t="n">
-        <v>7244381</v>
+        <v>7244500</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2321,6 +2331,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2329,21 +2344,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2363,7 +2363,7 @@
         <v>127727337</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>127727363</v>
       </c>
       <c r="B20" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127727387</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127727360</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>127727383</v>
       </c>
       <c r="B24" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>127727399</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>127727336</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>127727395</v>
       </c>
       <c r="B28" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727353</v>
+        <v>127727346</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538793</v>
+        <v>538953</v>
       </c>
       <c r="R29" t="n">
-        <v>7244570</v>
+        <v>7244425</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727346</v>
+        <v>127727353</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538953</v>
+        <v>538793</v>
       </c>
       <c r="R30" t="n">
-        <v>7244425</v>
+        <v>7244570</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3910,7 +3910,7 @@
         <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91701</v>
+        <v>91709</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727372</v>
+        <v>127727393</v>
       </c>
       <c r="B32" t="n">
-        <v>91337</v>
+        <v>91367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538755</v>
+        <v>538905</v>
       </c>
       <c r="R32" t="n">
-        <v>7244423</v>
+        <v>7244572</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Granstubbe och låga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe och låga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727393</v>
+        <v>127727358</v>
       </c>
       <c r="B33" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,34 +4152,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538905</v>
+        <v>538729</v>
       </c>
       <c r="R33" t="n">
-        <v>7244572</v>
+        <v>7244550</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4214,6 +4219,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4222,26 +4232,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4258,10 +4248,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727358</v>
+        <v>127727372</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,39 +4259,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538729</v>
+        <v>538755</v>
       </c>
       <c r="R34" t="n">
-        <v>7244550</v>
+        <v>7244423</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,11 +4321,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4349,6 +4329,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Granstubbe och låga</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe och låga</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R36" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R37" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4699,7 +4699,7 @@
         <v>127727368</v>
       </c>
       <c r="B38" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727330</v>
+        <v>127727384</v>
       </c>
       <c r="B39" t="n">
-        <v>91306</v>
+        <v>91759</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,21 +4814,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>538757</v>
+        <v>539028</v>
       </c>
       <c r="R39" t="n">
-        <v>7244545</v>
+        <v>7244444</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4897,12 +4897,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Toppknäckt gran</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Toppknäckt gran</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4920,10 +4920,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727384</v>
+        <v>127727330</v>
       </c>
       <c r="B40" t="n">
-        <v>91751</v>
+        <v>91314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539028</v>
+        <v>538757</v>
       </c>
       <c r="R40" t="n">
-        <v>7244444</v>
+        <v>7244545</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
         <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>127727361</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727349</v>
+        <v>127727398</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,39 +5262,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539183</v>
+        <v>538623</v>
       </c>
       <c r="R43" t="n">
-        <v>7244439</v>
+        <v>7244488</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5327,11 +5322,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5358,10 +5348,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5398,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R44" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5465,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727367</v>
+        <v>127727343</v>
       </c>
       <c r="B45" t="n">
-        <v>91637</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5476,34 +5466,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539047</v>
+        <v>538886</v>
       </c>
       <c r="R45" t="n">
-        <v>7244483</v>
+        <v>7244392</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5538,6 +5533,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5546,16 +5546,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5572,10 +5562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B46" t="n">
-        <v>79023</v>
+        <v>91645</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5583,21 +5573,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5607,10 +5597,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R46" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,6 +5643,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5672,7 +5672,7 @@
         <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R49" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,10 +6000,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R50" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,7 +6110,7 @@
         <v>127727339</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>127727371</v>
       </c>
       <c r="B52" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,32 +6320,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727379</v>
+        <v>127727334</v>
       </c>
       <c r="B53" t="n">
-        <v>91337</v>
+        <v>92046</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>538959</v>
+        <v>539146</v>
       </c>
       <c r="R53" t="n">
-        <v>7244418</v>
+        <v>7244417</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6435,7 +6435,7 @@
         <v>127727396</v>
       </c>
       <c r="B54" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6549,32 +6549,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727334</v>
+        <v>127727379</v>
       </c>
       <c r="B55" t="n">
-        <v>92038</v>
+        <v>91345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539146</v>
+        <v>538959</v>
       </c>
       <c r="R55" t="n">
-        <v>7244417</v>
+        <v>7244418</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R56" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,10 +6768,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B57" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R57" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727333</v>
+        <v>127727352</v>
       </c>
       <c r="B2" t="n">
-        <v>92046</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539048</v>
+        <v>539002</v>
       </c>
       <c r="R2" t="n">
-        <v>7244482</v>
+        <v>7244475</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,6 +753,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,26 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>stående 2stammig lutar</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # stående 2stammig lutar</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727389</v>
+        <v>127727333</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>92047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538633</v>
+        <v>539048</v>
       </c>
       <c r="R3" t="n">
-        <v>7244525</v>
+        <v>7244482</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,12 +876,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
+          <t>stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+          <t>Picea abies # stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727352</v>
+        <v>127727389</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539002</v>
+        <v>538633</v>
       </c>
       <c r="R4" t="n">
-        <v>7244475</v>
+        <v>7244525</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +972,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,6 +980,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727385</v>
+        <v>127727331</v>
       </c>
       <c r="B6" t="n">
-        <v>91363</v>
+        <v>92047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539028</v>
+        <v>539188</v>
       </c>
       <c r="R6" t="n">
-        <v>7244444</v>
+        <v>7244462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727394</v>
+        <v>127727377</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539095</v>
+        <v>539032</v>
       </c>
       <c r="R7" t="n">
-        <v>7244407</v>
+        <v>7244470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727331</v>
+        <v>127727385</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>91364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539188</v>
+        <v>539028</v>
       </c>
       <c r="R8" t="n">
-        <v>7244462</v>
+        <v>7244444</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727377</v>
+        <v>127727351</v>
       </c>
       <c r="B9" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539032</v>
+        <v>539184</v>
       </c>
       <c r="R9" t="n">
-        <v>7244470</v>
+        <v>7244459</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,6 +1547,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1550,26 +1560,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Ny rotvälta</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Ny rotvälta</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1586,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727341</v>
+        <v>127727347</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1626,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538761</v>
+        <v>539057</v>
       </c>
       <c r="R10" t="n">
-        <v>7244400</v>
+        <v>7244431</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727351</v>
+        <v>127727341</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1733,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539184</v>
+        <v>538761</v>
       </c>
       <c r="R11" t="n">
-        <v>7244459</v>
+        <v>7244400</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727347</v>
+        <v>127727394</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539057</v>
+        <v>539095</v>
       </c>
       <c r="R12" t="n">
-        <v>7244431</v>
+        <v>7244407</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1878,11 +1863,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,6 +1871,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1910,7 +1910,7 @@
         <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727378</v>
+        <v>127727375</v>
       </c>
       <c r="B14" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538857</v>
+        <v>539165</v>
       </c>
       <c r="R14" t="n">
-        <v>7244381</v>
+        <v>7244399</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,9 +2116,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2136,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727375</v>
+        <v>127727378</v>
       </c>
       <c r="B15" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539165</v>
+        <v>538857</v>
       </c>
       <c r="R15" t="n">
-        <v>7244399</v>
+        <v>7244381</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,14 +2233,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B21" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R21" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727387</v>
+        <v>127727360</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,34 +2930,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538961</v>
+        <v>538856</v>
       </c>
       <c r="R22" t="n">
-        <v>7244436</v>
+        <v>7244394</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2992,6 +2997,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3000,26 +3010,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>låga, knäckt nyfallen</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3036,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727360</v>
+        <v>127727376</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,39 +3037,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538856</v>
+        <v>539109</v>
       </c>
       <c r="R23" t="n">
-        <v>7244394</v>
+        <v>7244501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3114,11 +3099,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3127,6 +3107,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3146,7 +3146,7 @@
         <v>127727383</v>
       </c>
       <c r="B24" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727380</v>
+        <v>127727395</v>
       </c>
       <c r="B27" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
         <v>538993</v>
       </c>
       <c r="R27" t="n">
-        <v>7244440</v>
+        <v>7244472</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3556,9 +3556,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3576,10 +3581,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727395</v>
+        <v>127727353</v>
       </c>
       <c r="B28" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,34 +3592,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R28" t="n">
-        <v>7244472</v>
+        <v>7244570</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,6 +3659,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3657,26 +3672,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3800,10 +3795,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727353</v>
+        <v>127727380</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,39 +3806,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R30" t="n">
-        <v>7244570</v>
+        <v>7244440</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,11 +3868,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3876,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3910,7 +3910,7 @@
         <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727393</v>
+        <v>127727372</v>
       </c>
       <c r="B32" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538905</v>
+        <v>538755</v>
       </c>
       <c r="R32" t="n">
-        <v>7244572</v>
+        <v>7244423</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Granstubbe och låga</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Granstubbe och låga</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727358</v>
+        <v>127727393</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,39 +4152,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538729</v>
+        <v>538905</v>
       </c>
       <c r="R33" t="n">
-        <v>7244550</v>
+        <v>7244572</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,11 +4214,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4232,6 +4222,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4248,10 +4258,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727372</v>
+        <v>127727358</v>
       </c>
       <c r="B34" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,34 +4269,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538755</v>
+        <v>538729</v>
       </c>
       <c r="R34" t="n">
-        <v>7244423</v>
+        <v>7244550</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,6 +4336,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4329,26 +4349,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granstubbe och låga</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe och låga</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R36" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R37" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727368</v>
+        <v>127727384</v>
       </c>
       <c r="B38" t="n">
-        <v>91718</v>
+        <v>91760</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1506</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539047</v>
+        <v>539028</v>
       </c>
       <c r="R38" t="n">
-        <v>7244483</v>
+        <v>7244444</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4778,14 +4778,24 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4803,10 +4813,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727384</v>
+        <v>127727330</v>
       </c>
       <c r="B39" t="n">
-        <v>91759</v>
+        <v>91315</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,21 +4824,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4838,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539028</v>
+        <v>538757</v>
       </c>
       <c r="R39" t="n">
-        <v>7244444</v>
+        <v>7244545</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4897,12 +4907,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4920,45 +4930,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B40" t="n">
-        <v>91314</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R40" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4993,6 +5008,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5001,26 +5021,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5037,50 +5037,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727356</v>
+        <v>127727368</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91719</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538874</v>
+        <v>539047</v>
       </c>
       <c r="R41" t="n">
-        <v>7244402</v>
+        <v>7244483</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5115,11 +5110,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,6 +5118,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5348,7 +5348,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727349</v>
+        <v>127727343</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539183</v>
+        <v>538886</v>
       </c>
       <c r="R44" t="n">
-        <v>7244439</v>
+        <v>7244392</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R45" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5565,7 +5565,7 @@
         <v>127727367</v>
       </c>
       <c r="B46" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>88753</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,39 +5680,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R47" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5747,11 +5742,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5760,6 +5750,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5776,10 +5786,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>88752</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,34 +5797,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R48" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,6 +5864,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5857,26 +5877,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5893,7 +5893,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B49" t="n">
         <v>57672</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R49" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,7 +6000,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B50" t="n">
         <v>57672</v>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R50" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6323,7 +6323,7 @@
         <v>127727334</v>
       </c>
       <c r="B53" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727396</v>
+        <v>127727379</v>
       </c>
       <c r="B54" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6443,21 +6443,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539008</v>
+        <v>538959</v>
       </c>
       <c r="R54" t="n">
-        <v>7244491</v>
+        <v>7244418</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6524,14 +6524,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6549,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727379</v>
+        <v>127727396</v>
       </c>
       <c r="B55" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,21 +6555,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>538959</v>
+        <v>539008</v>
       </c>
       <c r="R55" t="n">
-        <v>7244418</v>
+        <v>7244491</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6641,9 +6636,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6692,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,7 +6768,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6799,7 +6799,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R57" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727331</v>
+        <v>127727377</v>
       </c>
       <c r="B6" t="n">
-        <v>92047</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539188</v>
+        <v>539032</v>
       </c>
       <c r="R6" t="n">
-        <v>7244462</v>
+        <v>7244470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727377</v>
+        <v>127727385</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>91364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539032</v>
+        <v>539028</v>
       </c>
       <c r="R7" t="n">
-        <v>7244470</v>
+        <v>7244444</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727385</v>
+        <v>127727394</v>
       </c>
       <c r="B8" t="n">
-        <v>91364</v>
+        <v>91368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539028</v>
+        <v>539095</v>
       </c>
       <c r="R8" t="n">
-        <v>7244444</v>
+        <v>7244407</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,50 +1469,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727351</v>
+        <v>127727331</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>92047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539184</v>
+        <v>539188</v>
       </c>
       <c r="R9" t="n">
-        <v>7244459</v>
+        <v>7244462</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,11 +1542,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1560,6 +1550,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1576,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727347</v>
+        <v>127727351</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1616,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539057</v>
+        <v>539184</v>
       </c>
       <c r="R10" t="n">
-        <v>7244431</v>
+        <v>7244459</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727341</v>
+        <v>127727347</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1723,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538761</v>
+        <v>539057</v>
       </c>
       <c r="R11" t="n">
-        <v>7244400</v>
+        <v>7244431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1790,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727394</v>
+        <v>127727341</v>
       </c>
       <c r="B12" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539095</v>
+        <v>538761</v>
       </c>
       <c r="R12" t="n">
-        <v>7244407</v>
+        <v>7244400</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,6 +1878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1871,26 +1891,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727374</v>
+        <v>127727357</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538600</v>
+        <v>539013</v>
       </c>
       <c r="R13" t="n">
-        <v>7244556</v>
+        <v>7244500</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,6 +1985,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1988,26 +1998,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående, död</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727375</v>
+        <v>127727337</v>
       </c>
       <c r="B14" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2025,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539165</v>
+        <v>538658</v>
       </c>
       <c r="R14" t="n">
-        <v>7244399</v>
+        <v>7244502</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2097,6 +2092,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2105,26 +2105,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2141,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727378</v>
+        <v>127727374</v>
       </c>
       <c r="B15" t="n">
         <v>91346</v>
@@ -2176,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538857</v>
+        <v>538600</v>
       </c>
       <c r="R15" t="n">
-        <v>7244381</v>
+        <v>7244556</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,9 +2213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2253,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727357</v>
+        <v>127727375</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,39 +2249,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539013</v>
+        <v>539165</v>
       </c>
       <c r="R16" t="n">
-        <v>7244500</v>
+        <v>7244399</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2331,11 +2311,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,6 +2319,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2360,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727337</v>
+        <v>127727378</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,39 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538658</v>
+        <v>538857</v>
       </c>
       <c r="R17" t="n">
-        <v>7244502</v>
+        <v>7244381</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2438,11 +2428,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2451,6 +2436,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R21" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R23" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727399</v>
+        <v>127727336</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,34 +3271,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538900</v>
+        <v>538852</v>
       </c>
       <c r="R25" t="n">
-        <v>7244576</v>
+        <v>7244404</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,6 +3336,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727336</v>
+        <v>127727399</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,39 +3378,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538852</v>
+        <v>538900</v>
       </c>
       <c r="R26" t="n">
-        <v>7244404</v>
+        <v>7244576</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3433,11 +3438,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727395</v>
+        <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
         <v>538993</v>
       </c>
       <c r="R27" t="n">
-        <v>7244472</v>
+        <v>7244440</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3556,14 +3556,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3795,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727380</v>
+        <v>127727395</v>
       </c>
       <c r="B30" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,21 +3801,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3833,7 +3828,7 @@
         <v>538993</v>
       </c>
       <c r="R30" t="n">
-        <v>7244440</v>
+        <v>7244472</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3887,9 +3882,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727393</v>
+        <v>127727358</v>
       </c>
       <c r="B33" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,34 +4152,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538905</v>
+        <v>538729</v>
       </c>
       <c r="R33" t="n">
-        <v>7244572</v>
+        <v>7244550</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4214,6 +4219,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4222,26 +4232,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4258,10 +4248,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727358</v>
+        <v>127727393</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,39 +4259,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538729</v>
+        <v>538905</v>
       </c>
       <c r="R34" t="n">
-        <v>7244550</v>
+        <v>7244572</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,11 +4321,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4349,6 +4329,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4813,32 +4813,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727330</v>
+        <v>127727368</v>
       </c>
       <c r="B39" t="n">
-        <v>91315</v>
+        <v>91719</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>538757</v>
+        <v>539047</v>
       </c>
       <c r="R39" t="n">
-        <v>7244545</v>
+        <v>7244483</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4895,24 +4895,14 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Toppknäckt gran</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Toppknäckt gran</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4930,50 +4920,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727356</v>
+        <v>127727330</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>91315</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538874</v>
+        <v>538757</v>
       </c>
       <c r="R40" t="n">
-        <v>7244402</v>
+        <v>7244545</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5008,11 +4993,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5021,6 +5001,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5037,45 +5037,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727368</v>
+        <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>91719</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539047</v>
+        <v>538874</v>
       </c>
       <c r="R41" t="n">
-        <v>7244483</v>
+        <v>7244402</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5110,6 +5115,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5118,16 +5128,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R43" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5332,6 +5332,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5348,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727343</v>
+        <v>127727398</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5359,39 +5369,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538886</v>
+        <v>538623</v>
       </c>
       <c r="R44" t="n">
-        <v>7244392</v>
+        <v>7244488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5424,11 +5429,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727349</v>
+        <v>127727343</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539183</v>
+        <v>538886</v>
       </c>
       <c r="R45" t="n">
-        <v>7244439</v>
+        <v>7244392</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727367</v>
+        <v>127727349</v>
       </c>
       <c r="B46" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5573,34 +5573,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539047</v>
+        <v>539183</v>
       </c>
       <c r="R46" t="n">
-        <v>7244483</v>
+        <v>7244439</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5635,6 +5640,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5643,16 +5653,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,10 +6135,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6147,10 +6151,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R51" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6183,11 +6187,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6213,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B52" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,16 +6224,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6242,14 +6241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R52" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6294,6 +6289,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6320,32 +6320,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727334</v>
+        <v>127727379</v>
       </c>
       <c r="B53" t="n">
-        <v>92047</v>
+        <v>91346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539146</v>
+        <v>538959</v>
       </c>
       <c r="R53" t="n">
-        <v>7244417</v>
+        <v>7244418</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6432,32 +6432,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727379</v>
+        <v>127727334</v>
       </c>
       <c r="B54" t="n">
-        <v>91346</v>
+        <v>92047</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538959</v>
+        <v>539146</v>
       </c>
       <c r="R54" t="n">
-        <v>7244418</v>
+        <v>7244417</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727396</v>
+        <v>127727355</v>
       </c>
       <c r="B55" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,31 +6555,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539008</v>
+        <v>538621</v>
       </c>
       <c r="R55" t="n">
         <v>7244491</v>
@@ -6617,6 +6622,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6625,26 +6635,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6661,7 +6651,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6692,7 +6682,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6691,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R56" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6731,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,10 +6758,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727348</v>
+        <v>127727396</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,39 +6769,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539079</v>
+        <v>539008</v>
       </c>
       <c r="R57" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6846,11 +6831,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6859,6 +6839,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727352</v>
+        <v>127727333</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539002</v>
+        <v>539048</v>
       </c>
       <c r="R2" t="n">
-        <v>7244475</v>
+        <v>7244482</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +748,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>stående 2stammig lutar</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # stående 2stammig lutar</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727333</v>
+        <v>127727389</v>
       </c>
       <c r="B3" t="n">
-        <v>92047</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539048</v>
+        <v>538633</v>
       </c>
       <c r="R3" t="n">
-        <v>7244482</v>
+        <v>7244525</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,12 +886,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>stående 2stammig lutar</t>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # stående 2stammig lutar</t>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727389</v>
+        <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538633</v>
+        <v>539002</v>
       </c>
       <c r="R4" t="n">
-        <v>7244525</v>
+        <v>7244475</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,6 +987,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -980,26 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727377</v>
+        <v>127727347</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,34 +1129,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539032</v>
+        <v>539057</v>
       </c>
       <c r="R6" t="n">
-        <v>7244470</v>
+        <v>7244431</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1191,6 +1196,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1199,26 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Ny rotvälta</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Ny rotvälta</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1235,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727385</v>
+        <v>127727341</v>
       </c>
       <c r="B7" t="n">
-        <v>91364</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539028</v>
+        <v>538761</v>
       </c>
       <c r="R7" t="n">
-        <v>7244444</v>
+        <v>7244400</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,6 +1303,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1316,26 +1316,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727394</v>
+        <v>127727377</v>
       </c>
       <c r="B8" t="n">
-        <v>91368</v>
+        <v>91347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539095</v>
+        <v>539032</v>
       </c>
       <c r="R8" t="n">
-        <v>7244407</v>
+        <v>7244470</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1426,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1472,7 +1452,7 @@
         <v>127727331</v>
       </c>
       <c r="B9" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727351</v>
+        <v>127727394</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,39 +1577,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539184</v>
+        <v>539095</v>
       </c>
       <c r="R10" t="n">
-        <v>7244459</v>
+        <v>7244407</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,11 +1639,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1677,6 +1647,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727347</v>
+        <v>127727385</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>91365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,39 +1694,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539057</v>
+        <v>539028</v>
       </c>
       <c r="R11" t="n">
-        <v>7244431</v>
+        <v>7244444</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,11 +1756,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1784,6 +1764,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727341</v>
+        <v>127727351</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538761</v>
+        <v>539184</v>
       </c>
       <c r="R12" t="n">
-        <v>7244400</v>
+        <v>7244459</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727357</v>
+        <v>127727337</v>
       </c>
       <c r="B13" t="n">
         <v>57672</v>
@@ -1938,7 +1938,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539013</v>
+        <v>538658</v>
       </c>
       <c r="R13" t="n">
-        <v>7244500</v>
+        <v>7244502</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727337</v>
+        <v>127727357</v>
       </c>
       <c r="B14" t="n">
         <v>57672</v>
@@ -2045,7 +2045,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538658</v>
+        <v>539013</v>
       </c>
       <c r="R14" t="n">
-        <v>7244502</v>
+        <v>7244500</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
         <v>127727374</v>
       </c>
       <c r="B15" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727375</v>
+        <v>127727378</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539165</v>
+        <v>538857</v>
       </c>
       <c r="R16" t="n">
-        <v>7244399</v>
+        <v>7244381</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,14 +2330,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2355,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727378</v>
+        <v>127727375</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538857</v>
+        <v>539165</v>
       </c>
       <c r="R17" t="n">
-        <v>7244381</v>
+        <v>7244399</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2447,9 +2442,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2805,7 +2805,7 @@
         <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727360</v>
+        <v>127727387</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,39 +2930,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538856</v>
+        <v>538961</v>
       </c>
       <c r="R22" t="n">
-        <v>7244394</v>
+        <v>7244436</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2997,11 +2992,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3010,6 +3000,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>låga, knäckt nyfallen</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # låga, knäckt nyfallen</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3026,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727387</v>
+        <v>127727360</v>
       </c>
       <c r="B23" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,34 +3047,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538961</v>
+        <v>538856</v>
       </c>
       <c r="R23" t="n">
-        <v>7244436</v>
+        <v>7244394</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,6 +3114,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3107,26 +3127,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>låga, knäckt nyfallen</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727383</v>
+        <v>127727336</v>
       </c>
       <c r="B24" t="n">
-        <v>91364</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,34 +3154,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538911</v>
+        <v>538852</v>
       </c>
       <c r="R24" t="n">
-        <v>7244544</v>
+        <v>7244404</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3216,6 +3221,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3224,26 +3234,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3260,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727336</v>
+        <v>127727383</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>91365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,39 +3261,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538852</v>
+        <v>538911</v>
       </c>
       <c r="R25" t="n">
-        <v>7244404</v>
+        <v>7244544</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3338,11 +3323,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3351,6 +3331,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3467,7 +3467,7 @@
         <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>127727395</v>
       </c>
       <c r="B30" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,45 +3907,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727386</v>
+        <v>127727358</v>
       </c>
       <c r="B31" t="n">
-        <v>91710</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538633</v>
+        <v>538729</v>
       </c>
       <c r="R31" t="n">
-        <v>7244525</v>
+        <v>7244550</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3980,6 +3985,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3988,26 +3998,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4027,7 +4017,7 @@
         <v>127727372</v>
       </c>
       <c r="B32" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,50 +4131,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727358</v>
+        <v>127727386</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538729</v>
+        <v>538633</v>
       </c>
       <c r="R33" t="n">
-        <v>7244550</v>
+        <v>7244525</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,11 +4204,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4232,6 +4212,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Grantickeporing på minst 4 grantickor</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4251,7 +4251,7 @@
         <v>127727393</v>
       </c>
       <c r="B34" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727384</v>
+        <v>127727330</v>
       </c>
       <c r="B38" t="n">
-        <v>91760</v>
+        <v>91316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539028</v>
+        <v>538757</v>
       </c>
       <c r="R38" t="n">
-        <v>7244444</v>
+        <v>7244545</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,12 +4790,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4813,45 +4813,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727368</v>
+        <v>127727356</v>
       </c>
       <c r="B39" t="n">
-        <v>91719</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539047</v>
+        <v>538874</v>
       </c>
       <c r="R39" t="n">
-        <v>7244483</v>
+        <v>7244402</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4886,6 +4891,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4894,16 +4904,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4920,32 +4920,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727330</v>
+        <v>127727368</v>
       </c>
       <c r="B40" t="n">
-        <v>91315</v>
+        <v>91720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538757</v>
+        <v>539047</v>
       </c>
       <c r="R40" t="n">
-        <v>7244545</v>
+        <v>7244483</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5002,24 +5002,14 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Toppknäckt gran</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Toppknäckt gran</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5037,50 +5027,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727356</v>
+        <v>127727384</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91761</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538874</v>
+        <v>539028</v>
       </c>
       <c r="R41" t="n">
-        <v>7244402</v>
+        <v>7244444</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5115,11 +5100,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,6 +5108,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727367</v>
+        <v>127727398</v>
       </c>
       <c r="B43" t="n">
-        <v>91646</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539047</v>
+        <v>538623</v>
       </c>
       <c r="R43" t="n">
-        <v>7244483</v>
+        <v>7244488</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5332,16 +5332,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5348,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727398</v>
+        <v>127727343</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,34 +5359,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538623</v>
+        <v>538886</v>
       </c>
       <c r="R44" t="n">
-        <v>7244488</v>
+        <v>7244392</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,6 +5424,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R45" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727349</v>
+        <v>127727367</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5573,39 +5573,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539183</v>
+        <v>539047</v>
       </c>
       <c r="R46" t="n">
-        <v>7244439</v>
+        <v>7244483</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5640,11 +5635,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5653,6 +5643,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5672,7 +5672,7 @@
         <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B49" t="n">
         <v>57672</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R49" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,7 +6000,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B50" t="n">
         <v>57672</v>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R50" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6323,7 +6323,7 @@
         <v>127727379</v>
       </c>
       <c r="B53" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>127727334</v>
       </c>
       <c r="B54" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B55" t="n">
         <v>57672</v>
@@ -6575,7 +6575,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R55" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6651,7 +6651,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6682,7 +6682,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6761,7 +6761,7 @@
         <v>127727396</v>
       </c>
       <c r="B57" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727333</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727389</v>
+        <v>127727352</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538633</v>
+        <v>539002</v>
       </c>
       <c r="R3" t="n">
-        <v>7244525</v>
+        <v>7244475</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +870,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,26 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727352</v>
+        <v>127727369</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>58042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +930,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539002</v>
+        <v>538906</v>
       </c>
       <c r="R4" t="n">
-        <v>7244475</v>
+        <v>7244545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,11 +975,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727369</v>
+        <v>127727389</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538906</v>
+        <v>538633</v>
       </c>
       <c r="R5" t="n">
-        <v>7244545</v>
+        <v>7244525</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,6 +1082,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,50 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727347</v>
+        <v>127727331</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539057</v>
+        <v>539188</v>
       </c>
       <c r="R6" t="n">
-        <v>7244431</v>
+        <v>7244462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,11 +1191,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1209,6 +1199,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1332,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727377</v>
+        <v>127727351</v>
       </c>
       <c r="B8" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1353,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539032</v>
+        <v>539184</v>
       </c>
       <c r="R8" t="n">
-        <v>7244470</v>
+        <v>7244459</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1405,6 +1420,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1413,26 +1433,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Ny rotvälta</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Ny rotvälta</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1449,45 +1449,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727331</v>
+        <v>127727347</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539188</v>
+        <v>539057</v>
       </c>
       <c r="R9" t="n">
-        <v>7244462</v>
+        <v>7244431</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1527,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1530,26 +1540,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1566,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727394</v>
+        <v>127727377</v>
       </c>
       <c r="B10" t="n">
-        <v>91369</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539095</v>
+        <v>539032</v>
       </c>
       <c r="R10" t="n">
-        <v>7244407</v>
+        <v>7244470</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1660,12 +1650,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1686,7 +1676,7 @@
         <v>127727385</v>
       </c>
       <c r="B11" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727351</v>
+        <v>127727394</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539184</v>
+        <v>539095</v>
       </c>
       <c r="R12" t="n">
-        <v>7244459</v>
+        <v>7244407</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1878,11 +1863,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,6 +1871,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727337</v>
+        <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538658</v>
+        <v>538600</v>
       </c>
       <c r="R13" t="n">
-        <v>7244502</v>
+        <v>7244556</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,11 +1980,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,6 +1988,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående, död</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2014,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727357</v>
+        <v>127727375</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,39 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539013</v>
+        <v>539165</v>
       </c>
       <c r="R14" t="n">
-        <v>7244500</v>
+        <v>7244399</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2092,11 +2097,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2105,6 +2105,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2121,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727374</v>
+        <v>127727378</v>
       </c>
       <c r="B15" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538600</v>
+        <v>538857</v>
       </c>
       <c r="R15" t="n">
-        <v>7244556</v>
+        <v>7244381</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2213,14 +2233,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727378</v>
+        <v>127727357</v>
       </c>
       <c r="B16" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,34 +2264,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538857</v>
+        <v>539013</v>
       </c>
       <c r="R16" t="n">
-        <v>7244381</v>
+        <v>7244500</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2311,6 +2331,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2319,21 +2344,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2350,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727375</v>
+        <v>127727337</v>
       </c>
       <c r="B17" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,34 +2371,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539165</v>
+        <v>538658</v>
       </c>
       <c r="R17" t="n">
-        <v>7244399</v>
+        <v>7244502</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2423,6 +2438,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2431,26 +2451,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2470,7 +2470,7 @@
         <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727387</v>
+        <v>127727360</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,34 +2930,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538961</v>
+        <v>538856</v>
       </c>
       <c r="R22" t="n">
-        <v>7244436</v>
+        <v>7244394</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2992,6 +2997,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3000,26 +3010,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>låga, knäckt nyfallen</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3036,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727360</v>
+        <v>127727387</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,39 +3037,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538856</v>
+        <v>538961</v>
       </c>
       <c r="R23" t="n">
-        <v>7244394</v>
+        <v>7244436</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3114,11 +3099,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3127,6 +3107,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>låga, knäckt nyfallen</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # låga, knäckt nyfallen</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727336</v>
+        <v>127727383</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,39 +3154,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538852</v>
+        <v>538911</v>
       </c>
       <c r="R24" t="n">
-        <v>7244404</v>
+        <v>7244544</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3221,11 +3216,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3234,6 +3224,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3250,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727383</v>
+        <v>127727399</v>
       </c>
       <c r="B25" t="n">
-        <v>91365</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,21 +3271,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538911</v>
+        <v>538900</v>
       </c>
       <c r="R25" t="n">
-        <v>7244544</v>
+        <v>7244576</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,26 +3341,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3367,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727399</v>
+        <v>127727336</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,34 +3368,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538900</v>
+        <v>538852</v>
       </c>
       <c r="R26" t="n">
-        <v>7244576</v>
+        <v>7244404</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3438,6 +3433,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,7 +3467,7 @@
         <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727353</v>
+        <v>127727395</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,39 +3587,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R28" t="n">
-        <v>7244570</v>
+        <v>7244472</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3654,11 +3649,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3667,6 +3657,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3790,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727395</v>
+        <v>127727353</v>
       </c>
       <c r="B30" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,34 +3811,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R30" t="n">
-        <v>7244472</v>
+        <v>7244570</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3863,6 +3878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3871,26 +3891,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3907,50 +3907,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727358</v>
+        <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538729</v>
+        <v>538633</v>
       </c>
       <c r="R31" t="n">
-        <v>7244550</v>
+        <v>7244525</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3985,11 +3980,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3998,6 +3988,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Grantickeporing på minst 4 grantickor</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4017,7 +4027,7 @@
         <v>127727372</v>
       </c>
       <c r="B32" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,32 +4141,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727386</v>
+        <v>127727393</v>
       </c>
       <c r="B33" t="n">
-        <v>91711</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4166,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538633</v>
+        <v>538905</v>
       </c>
       <c r="R33" t="n">
-        <v>7244525</v>
+        <v>7244572</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4215,22 +4225,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4248,10 +4258,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727393</v>
+        <v>127727358</v>
       </c>
       <c r="B34" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,34 +4269,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538905</v>
+        <v>538729</v>
       </c>
       <c r="R34" t="n">
-        <v>7244572</v>
+        <v>7244550</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,6 +4336,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4329,26 +4349,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R36" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R37" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727330</v>
+        <v>127727384</v>
       </c>
       <c r="B38" t="n">
-        <v>91316</v>
+        <v>91762</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>538757</v>
+        <v>539028</v>
       </c>
       <c r="R38" t="n">
-        <v>7244545</v>
+        <v>7244444</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,12 +4790,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Toppknäckt gran</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # Toppknäckt gran</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4813,50 +4813,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727356</v>
+        <v>127727368</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91721</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>538874</v>
+        <v>539047</v>
       </c>
       <c r="R39" t="n">
-        <v>7244402</v>
+        <v>7244483</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4891,11 +4886,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4904,6 +4894,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4920,32 +4920,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727368</v>
+        <v>127727330</v>
       </c>
       <c r="B40" t="n">
-        <v>91720</v>
+        <v>91317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539047</v>
+        <v>538757</v>
       </c>
       <c r="R40" t="n">
-        <v>7244483</v>
+        <v>7244545</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5002,14 +5002,24 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5027,45 +5037,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727384</v>
+        <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>91761</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539028</v>
+        <v>538874</v>
       </c>
       <c r="R41" t="n">
-        <v>7244444</v>
+        <v>7244402</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,6 +5115,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5108,26 +5128,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R43" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5332,6 +5332,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5348,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727343</v>
+        <v>127727398</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5359,39 +5369,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538886</v>
+        <v>538623</v>
       </c>
       <c r="R44" t="n">
-        <v>7244392</v>
+        <v>7244488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5424,11 +5429,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727367</v>
+        <v>127727343</v>
       </c>
       <c r="B46" t="n">
-        <v>91647</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5573,34 +5573,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539047</v>
+        <v>538886</v>
       </c>
       <c r="R46" t="n">
-        <v>7244483</v>
+        <v>7244392</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5635,6 +5640,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5643,16 +5653,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>88754</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,34 +5680,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R47" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,6 +5747,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5760,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R48" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5864,11 +5849,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,6 +5857,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B51" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,14 +6135,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6151,10 +6147,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R51" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6187,6 +6183,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6213,10 +6214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6224,16 +6225,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6241,10 +6242,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R52" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6289,11 +6294,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6323,7 +6323,7 @@
         <v>127727379</v>
       </c>
       <c r="B53" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6432,32 +6432,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727334</v>
+        <v>127727396</v>
       </c>
       <c r="B54" t="n">
-        <v>92048</v>
+        <v>91370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539146</v>
+        <v>539008</v>
       </c>
       <c r="R54" t="n">
-        <v>7244417</v>
+        <v>7244491</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6524,9 +6524,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6544,50 +6549,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727348</v>
+        <v>127727334</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539079</v>
+        <v>539146</v>
       </c>
       <c r="R55" t="n">
-        <v>7244407</v>
+        <v>7244417</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6622,11 +6622,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6635,6 +6630,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6651,7 +6661,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6682,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6691,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R56" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6731,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6758,10 +6768,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727396</v>
+        <v>127727355</v>
       </c>
       <c r="B57" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6769,31 +6779,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539008</v>
+        <v>538621</v>
       </c>
       <c r="R57" t="n">
         <v>7244491</v>
@@ -6831,6 +6846,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6839,26 +6859,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727352</v>
+        <v>127727389</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539002</v>
+        <v>538633</v>
       </c>
       <c r="R3" t="n">
-        <v>7244475</v>
+        <v>7244525</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,11 +865,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,27 +909,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727369</v>
+        <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538906</v>
+        <v>539002</v>
       </c>
       <c r="R4" t="n">
-        <v>7244545</v>
+        <v>7244475</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,6 +985,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,45 +1016,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727389</v>
+        <v>127727369</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538633</v>
+        <v>538906</v>
       </c>
       <c r="R5" t="n">
-        <v>7244525</v>
+        <v>7244545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,26 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727331</v>
+        <v>127727377</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539188</v>
+        <v>539032</v>
       </c>
       <c r="R6" t="n">
-        <v>7244462</v>
+        <v>7244470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727341</v>
+        <v>127727385</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,39 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538761</v>
+        <v>539028</v>
       </c>
       <c r="R7" t="n">
-        <v>7244400</v>
+        <v>7244444</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,11 +1308,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1326,6 +1316,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1342,50 +1352,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727351</v>
+        <v>127727331</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539184</v>
+        <v>539188</v>
       </c>
       <c r="R8" t="n">
-        <v>7244459</v>
+        <v>7244462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,11 +1425,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1433,6 +1433,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1449,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727347</v>
+        <v>127727394</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,39 +1480,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539057</v>
+        <v>539095</v>
       </c>
       <c r="R9" t="n">
-        <v>7244431</v>
+        <v>7244407</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1527,11 +1542,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1540,6 +1550,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727377</v>
+        <v>127727351</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539032</v>
+        <v>539184</v>
       </c>
       <c r="R10" t="n">
-        <v>7244470</v>
+        <v>7244459</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,6 +1664,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1637,26 +1677,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Ny rotvälta</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # Ny rotvälta</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1673,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727385</v>
+        <v>127727347</v>
       </c>
       <c r="B11" t="n">
-        <v>91366</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,34 +1704,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539028</v>
+        <v>539057</v>
       </c>
       <c r="R11" t="n">
-        <v>7244444</v>
+        <v>7244431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,6 +1771,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1754,26 +1784,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1790,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727394</v>
+        <v>127727341</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539095</v>
+        <v>538761</v>
       </c>
       <c r="R12" t="n">
-        <v>7244407</v>
+        <v>7244400</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,6 +1878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1871,26 +1891,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R21" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R23" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727346</v>
+        <v>127727353</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538953</v>
+        <v>538793</v>
       </c>
       <c r="R29" t="n">
-        <v>7244425</v>
+        <v>7244570</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727353</v>
+        <v>127727346</v>
       </c>
       <c r="B30" t="n">
         <v>57672</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538793</v>
+        <v>538953</v>
       </c>
       <c r="R30" t="n">
-        <v>7244570</v>
+        <v>7244425</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727386</v>
+        <v>127727372</v>
       </c>
       <c r="B31" t="n">
-        <v>91712</v>
+        <v>91348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538633</v>
+        <v>538755</v>
       </c>
       <c r="R31" t="n">
-        <v>7244525</v>
+        <v>7244423</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granstubbe och låga</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granstubbe och låga</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727372</v>
+        <v>127727386</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>91712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538755</v>
+        <v>538633</v>
       </c>
       <c r="R32" t="n">
-        <v>7244423</v>
+        <v>7244525</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Granstubbe och låga</t>
+          <t>Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe och låga</t>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727393</v>
+        <v>127727358</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,34 +4152,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538905</v>
+        <v>538729</v>
       </c>
       <c r="R33" t="n">
-        <v>7244572</v>
+        <v>7244550</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4214,6 +4219,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4222,26 +4232,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4258,10 +4248,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727358</v>
+        <v>127727393</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,39 +4259,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538729</v>
+        <v>538905</v>
       </c>
       <c r="R34" t="n">
-        <v>7244550</v>
+        <v>7244572</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,11 +4321,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4349,6 +4329,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4482,7 +4482,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R36" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R37" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727384</v>
+        <v>127727368</v>
       </c>
       <c r="B38" t="n">
-        <v>91762</v>
+        <v>91721</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539028</v>
+        <v>539047</v>
       </c>
       <c r="R38" t="n">
-        <v>7244444</v>
+        <v>7244483</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4778,24 +4778,14 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4813,32 +4803,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727368</v>
+        <v>127727384</v>
       </c>
       <c r="B39" t="n">
-        <v>91721</v>
+        <v>91762</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1506</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4848,10 +4838,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539047</v>
+        <v>539028</v>
       </c>
       <c r="R39" t="n">
-        <v>7244483</v>
+        <v>7244444</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4895,14 +4885,24 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727349</v>
+        <v>127727343</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539183</v>
+        <v>538886</v>
       </c>
       <c r="R45" t="n">
-        <v>7244439</v>
+        <v>7244392</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R46" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B49" t="n">
         <v>57672</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R49" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,7 +6000,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B50" t="n">
         <v>57672</v>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R50" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,10 +6135,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6147,10 +6151,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R51" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6183,11 +6187,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6213,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B52" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,16 +6224,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6242,14 +6241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R52" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6294,6 +6289,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6432,32 +6432,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727396</v>
+        <v>127727334</v>
       </c>
       <c r="B54" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539008</v>
+        <v>539146</v>
       </c>
       <c r="R54" t="n">
-        <v>7244491</v>
+        <v>7244417</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6524,14 +6524,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6549,32 +6544,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727334</v>
+        <v>127727396</v>
       </c>
       <c r="B55" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539146</v>
+        <v>539008</v>
       </c>
       <c r="R55" t="n">
-        <v>7244417</v>
+        <v>7244491</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6641,9 +6636,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6692,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,7 +6768,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6799,7 +6799,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R57" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727377</v>
+        <v>127727331</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539032</v>
+        <v>539188</v>
       </c>
       <c r="R6" t="n">
-        <v>7244470</v>
+        <v>7244462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727385</v>
+        <v>127727377</v>
       </c>
       <c r="B7" t="n">
-        <v>91366</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539028</v>
+        <v>539032</v>
       </c>
       <c r="R7" t="n">
-        <v>7244444</v>
+        <v>7244470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727331</v>
+        <v>127727385</v>
       </c>
       <c r="B8" t="n">
-        <v>92049</v>
+        <v>91366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539188</v>
+        <v>539028</v>
       </c>
       <c r="R8" t="n">
-        <v>7244462</v>
+        <v>7244444</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -4696,32 +4696,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727368</v>
+        <v>127727330</v>
       </c>
       <c r="B38" t="n">
-        <v>91721</v>
+        <v>91317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1506</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539047</v>
+        <v>538757</v>
       </c>
       <c r="R38" t="n">
-        <v>7244483</v>
+        <v>7244545</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4778,14 +4778,24 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4803,32 +4813,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727384</v>
+        <v>127727368</v>
       </c>
       <c r="B39" t="n">
-        <v>91762</v>
+        <v>91721</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4838,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539028</v>
+        <v>539047</v>
       </c>
       <c r="R39" t="n">
-        <v>7244444</v>
+        <v>7244483</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4885,24 +4895,14 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4920,10 +4920,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727330</v>
+        <v>127727384</v>
       </c>
       <c r="B40" t="n">
-        <v>91317</v>
+        <v>91762</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538757</v>
+        <v>539028</v>
       </c>
       <c r="R40" t="n">
-        <v>7244545</v>
+        <v>7244444</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Toppknäckt gran</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Toppknäckt gran</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727367</v>
+        <v>127727343</v>
       </c>
       <c r="B43" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,34 +5262,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539047</v>
+        <v>538886</v>
       </c>
       <c r="R43" t="n">
-        <v>7244483</v>
+        <v>7244392</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5329,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,16 +5342,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R44" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5439,6 +5439,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5455,10 +5465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727343</v>
+        <v>127727398</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,39 +5476,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538886</v>
+        <v>538623</v>
       </c>
       <c r="R45" t="n">
-        <v>7244392</v>
+        <v>7244488</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5531,11 +5536,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,39 +5680,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R47" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5747,11 +5742,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5760,6 +5750,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5776,10 +5786,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>88755</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,34 +5797,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R48" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,6 +5864,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5857,26 +5877,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727331</v>
+        <v>127727377</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539188</v>
+        <v>539032</v>
       </c>
       <c r="R6" t="n">
-        <v>7244462</v>
+        <v>7244470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727377</v>
+        <v>127727385</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539032</v>
+        <v>539028</v>
       </c>
       <c r="R7" t="n">
-        <v>7244470</v>
+        <v>7244444</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727385</v>
+        <v>127727331</v>
       </c>
       <c r="B8" t="n">
-        <v>91366</v>
+        <v>92049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539028</v>
+        <v>539188</v>
       </c>
       <c r="R8" t="n">
-        <v>7244444</v>
+        <v>7244462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727387</v>
+        <v>127727360</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,34 +2813,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538961</v>
+        <v>538856</v>
       </c>
       <c r="R21" t="n">
-        <v>7244436</v>
+        <v>7244394</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2875,6 +2880,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2883,26 +2893,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>låga, knäckt nyfallen</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2919,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727360</v>
+        <v>127727376</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,39 +2920,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538856</v>
+        <v>539109</v>
       </c>
       <c r="R22" t="n">
-        <v>7244394</v>
+        <v>7244501</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2997,11 +2982,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3010,6 +2990,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R23" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727396</v>
+        <v>127727355</v>
       </c>
       <c r="B55" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,31 +6555,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539008</v>
+        <v>538621</v>
       </c>
       <c r="R55" t="n">
         <v>7244491</v>
@@ -6617,6 +6622,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6625,26 +6635,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6661,7 +6651,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6692,7 +6682,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6691,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R56" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6731,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,10 +6758,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727348</v>
+        <v>127727396</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,39 +6769,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539079</v>
+        <v>539008</v>
       </c>
       <c r="R57" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6846,11 +6831,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6859,6 +6839,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727389</v>
+        <v>127727352</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538633</v>
+        <v>539002</v>
       </c>
       <c r="R3" t="n">
-        <v>7244525</v>
+        <v>7244475</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +870,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,26 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727352</v>
+        <v>127727369</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>58042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +930,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539002</v>
+        <v>538906</v>
       </c>
       <c r="R4" t="n">
-        <v>7244475</v>
+        <v>7244545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,11 +975,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727369</v>
+        <v>127727389</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538906</v>
+        <v>538633</v>
       </c>
       <c r="R5" t="n">
-        <v>7244545</v>
+        <v>7244525</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,6 +1082,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727377</v>
+        <v>127727331</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539032</v>
+        <v>539188</v>
       </c>
       <c r="R6" t="n">
-        <v>7244470</v>
+        <v>7244462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727385</v>
+        <v>127727377</v>
       </c>
       <c r="B7" t="n">
-        <v>91366</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539028</v>
+        <v>539032</v>
       </c>
       <c r="R7" t="n">
-        <v>7244444</v>
+        <v>7244470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727331</v>
+        <v>127727385</v>
       </c>
       <c r="B8" t="n">
-        <v>92049</v>
+        <v>91366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539188</v>
+        <v>539028</v>
       </c>
       <c r="R8" t="n">
-        <v>7244462</v>
+        <v>7244444</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727360</v>
+        <v>127727387</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,39 +2813,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538856</v>
+        <v>538961</v>
       </c>
       <c r="R21" t="n">
-        <v>7244394</v>
+        <v>7244436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2880,11 +2875,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2893,6 +2883,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>låga, knäckt nyfallen</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # låga, knäckt nyfallen</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2909,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727376</v>
+        <v>127727360</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,34 +2930,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539109</v>
+        <v>538856</v>
       </c>
       <c r="R22" t="n">
-        <v>7244501</v>
+        <v>7244394</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2982,6 +2997,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2990,26 +3010,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R23" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727330</v>
+        <v>127727368</v>
       </c>
       <c r="B38" t="n">
-        <v>91317</v>
+        <v>91721</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>538757</v>
+        <v>539047</v>
       </c>
       <c r="R38" t="n">
-        <v>7244545</v>
+        <v>7244483</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4778,24 +4778,14 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Toppknäckt gran</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # Toppknäckt gran</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4813,32 +4803,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727368</v>
+        <v>127727384</v>
       </c>
       <c r="B39" t="n">
-        <v>91721</v>
+        <v>91762</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1506</v>
+        <v>4217</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4848,10 +4838,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539047</v>
+        <v>539028</v>
       </c>
       <c r="R39" t="n">
-        <v>7244483</v>
+        <v>7244444</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4895,14 +4885,24 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4920,45 +4920,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727384</v>
+        <v>127727356</v>
       </c>
       <c r="B40" t="n">
-        <v>91762</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539028</v>
+        <v>538874</v>
       </c>
       <c r="R40" t="n">
-        <v>7244444</v>
+        <v>7244402</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4993,6 +4998,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5001,26 +5011,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5037,50 +5027,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727356</v>
+        <v>127727330</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538874</v>
+        <v>538757</v>
       </c>
       <c r="R41" t="n">
-        <v>7244402</v>
+        <v>7244545</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5115,11 +5100,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,6 +5108,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727343</v>
+        <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,39 +5262,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538886</v>
+        <v>539047</v>
       </c>
       <c r="R43" t="n">
-        <v>7244392</v>
+        <v>7244483</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5329,11 +5324,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5342,6 +5332,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727367</v>
+        <v>127727398</v>
       </c>
       <c r="B44" t="n">
-        <v>91648</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539047</v>
+        <v>538623</v>
       </c>
       <c r="R44" t="n">
-        <v>7244483</v>
+        <v>7244488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5439,16 +5439,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5465,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727398</v>
+        <v>127727343</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5476,34 +5466,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538623</v>
+        <v>538886</v>
       </c>
       <c r="R45" t="n">
-        <v>7244488</v>
+        <v>7244392</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5536,6 +5531,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>88755</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,34 +5680,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R47" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,6 +5747,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5760,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R48" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5864,11 +5849,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,6 +5857,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727331</v>
+        <v>127727377</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539188</v>
+        <v>539032</v>
       </c>
       <c r="R6" t="n">
-        <v>7244462</v>
+        <v>7244470</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727377</v>
+        <v>127727385</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539032</v>
+        <v>539028</v>
       </c>
       <c r="R7" t="n">
-        <v>7244470</v>
+        <v>7244444</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727385</v>
+        <v>127727331</v>
       </c>
       <c r="B8" t="n">
-        <v>91366</v>
+        <v>92049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539028</v>
+        <v>539188</v>
       </c>
       <c r="R8" t="n">
-        <v>7244444</v>
+        <v>7244462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727387</v>
+        <v>127727360</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,34 +2813,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538961</v>
+        <v>538856</v>
       </c>
       <c r="R21" t="n">
-        <v>7244436</v>
+        <v>7244394</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2875,6 +2880,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2883,26 +2893,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>låga, knäckt nyfallen</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2919,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727360</v>
+        <v>127727376</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,39 +2920,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538856</v>
+        <v>539109</v>
       </c>
       <c r="R22" t="n">
-        <v>7244394</v>
+        <v>7244501</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2997,11 +2982,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3010,6 +2990,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R23" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727367</v>
+        <v>127727343</v>
       </c>
       <c r="B43" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,34 +5262,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539047</v>
+        <v>538886</v>
       </c>
       <c r="R43" t="n">
-        <v>7244483</v>
+        <v>7244392</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5329,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,16 +5342,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727398</v>
+        <v>127727367</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538623</v>
+        <v>539047</v>
       </c>
       <c r="R44" t="n">
-        <v>7244488</v>
+        <v>7244483</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5439,6 +5439,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5455,10 +5465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727343</v>
+        <v>127727398</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,39 +5476,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538886</v>
+        <v>538623</v>
       </c>
       <c r="R45" t="n">
-        <v>7244392</v>
+        <v>7244488</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5531,11 +5536,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,39 +5680,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R47" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5747,11 +5742,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5760,6 +5750,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5776,10 +5786,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>88755</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,34 +5797,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R48" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,6 +5864,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5857,26 +5877,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727360</v>
+        <v>127727387</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,39 +2813,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538856</v>
+        <v>538961</v>
       </c>
       <c r="R21" t="n">
-        <v>7244394</v>
+        <v>7244436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2880,11 +2875,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2893,6 +2883,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>låga, knäckt nyfallen</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # låga, knäckt nyfallen</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2909,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727376</v>
+        <v>127727360</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,34 +2930,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539109</v>
+        <v>538856</v>
       </c>
       <c r="R22" t="n">
-        <v>7244501</v>
+        <v>7244394</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2982,6 +2997,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2990,26 +3010,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R23" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4920,50 +4920,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727356</v>
+        <v>127727330</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>91317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538874</v>
+        <v>538757</v>
       </c>
       <c r="R40" t="n">
-        <v>7244402</v>
+        <v>7244545</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4998,11 +4993,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5011,6 +5001,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5027,45 +5037,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>91317</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R41" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,6 +5115,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5108,26 +5128,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>88755</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,34 +5680,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R47" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,6 +5747,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5760,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R48" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5864,11 +5849,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,6 +5857,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B51" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,14 +6135,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6151,10 +6147,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R51" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6187,6 +6183,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6213,10 +6214,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6224,16 +6225,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6241,10 +6242,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R52" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6289,11 +6294,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6544,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727355</v>
+        <v>127727396</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,36 +6555,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>538621</v>
+        <v>539008</v>
       </c>
       <c r="R55" t="n">
         <v>7244491</v>
@@ -6622,11 +6617,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack, rikligt</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6635,6 +6625,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6651,7 +6661,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6682,7 +6692,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6691,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6731,7 +6741,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6758,10 +6768,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727396</v>
+        <v>127727348</v>
       </c>
       <c r="B57" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6769,34 +6779,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539008</v>
+        <v>539079</v>
       </c>
       <c r="R57" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6831,6 +6846,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6839,26 +6859,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727352</v>
+        <v>127727389</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539002</v>
+        <v>538633</v>
       </c>
       <c r="R3" t="n">
-        <v>7244475</v>
+        <v>7244525</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,11 +865,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,27 +909,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727369</v>
+        <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538906</v>
+        <v>539002</v>
       </c>
       <c r="R4" t="n">
-        <v>7244545</v>
+        <v>7244475</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,6 +985,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,45 +1016,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727389</v>
+        <v>127727369</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538633</v>
+        <v>538906</v>
       </c>
       <c r="R5" t="n">
-        <v>7244525</v>
+        <v>7244545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,26 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -4920,45 +4920,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B40" t="n">
-        <v>91317</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R40" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4993,6 +4998,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5001,26 +5011,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5037,50 +5027,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727356</v>
+        <v>127727330</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538874</v>
+        <v>538757</v>
       </c>
       <c r="R41" t="n">
-        <v>7244402</v>
+        <v>7244545</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5115,11 +5100,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,6 +5108,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5251,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727343</v>
+        <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,39 +5262,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>538886</v>
+        <v>539047</v>
       </c>
       <c r="R43" t="n">
-        <v>7244392</v>
+        <v>7244483</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5329,11 +5324,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5342,6 +5332,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727367</v>
+        <v>127727398</v>
       </c>
       <c r="B44" t="n">
-        <v>91648</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539047</v>
+        <v>538623</v>
       </c>
       <c r="R44" t="n">
-        <v>7244483</v>
+        <v>7244488</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5439,16 +5439,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5465,10 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727398</v>
+        <v>127727343</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5476,34 +5466,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538623</v>
+        <v>538886</v>
       </c>
       <c r="R45" t="n">
-        <v>7244488</v>
+        <v>7244392</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5536,6 +5531,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,39 +5680,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R47" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5747,11 +5742,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5760,6 +5750,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5776,10 +5786,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>88755</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,34 +5797,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R48" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,6 +5864,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5857,26 +5877,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6544,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727396</v>
+        <v>127727355</v>
       </c>
       <c r="B55" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,31 +6555,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539008</v>
+        <v>538621</v>
       </c>
       <c r="R55" t="n">
         <v>7244491</v>
@@ -6617,6 +6622,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6625,26 +6635,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6661,7 +6651,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6692,7 +6682,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6701,10 +6691,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R56" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,7 +6731,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,10 +6758,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727348</v>
+        <v>127727396</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,39 +6769,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539079</v>
+        <v>539008</v>
       </c>
       <c r="R57" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6846,11 +6831,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6859,6 +6839,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727333</v>
+        <v>127727389</v>
       </c>
       <c r="B2" t="n">
-        <v>92049</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539048</v>
+        <v>538633</v>
       </c>
       <c r="R2" t="n">
-        <v>7244482</v>
+        <v>7244525</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>stående 2stammig lutar</t>
+          <t>Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # stående 2stammig lutar</t>
+          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727389</v>
+        <v>127727333</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>92057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538633</v>
+        <v>539048</v>
       </c>
       <c r="R3" t="n">
-        <v>7244525</v>
+        <v>7244482</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
+          <t>stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+          <t>Picea abies # stående 2stammig lutar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>127727369</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727377</v>
+        <v>127727394</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539032</v>
+        <v>539095</v>
       </c>
       <c r="R6" t="n">
-        <v>7244470</v>
+        <v>7244407</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727385</v>
+        <v>127727377</v>
       </c>
       <c r="B7" t="n">
-        <v>91366</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539028</v>
+        <v>539032</v>
       </c>
       <c r="R7" t="n">
-        <v>7244444</v>
+        <v>7244470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727331</v>
+        <v>127727385</v>
       </c>
       <c r="B8" t="n">
-        <v>92049</v>
+        <v>91374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539188</v>
+        <v>539028</v>
       </c>
       <c r="R8" t="n">
-        <v>7244462</v>
+        <v>7244444</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727394</v>
+        <v>127727341</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539095</v>
+        <v>538761</v>
       </c>
       <c r="R9" t="n">
-        <v>7244407</v>
+        <v>7244400</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,6 +1547,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1550,26 +1560,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1589,7 +1579,7 @@
         <v>127727351</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1686,7 @@
         <v>127727347</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,50 +1790,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727341</v>
+        <v>127727331</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>92057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538761</v>
+        <v>539188</v>
       </c>
       <c r="R12" t="n">
-        <v>7244400</v>
+        <v>7244462</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1878,11 +1863,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,6 +1871,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727374</v>
+        <v>127727357</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538600</v>
+        <v>539013</v>
       </c>
       <c r="R13" t="n">
-        <v>7244556</v>
+        <v>7244500</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,6 +1985,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1988,26 +1998,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående, död</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727375</v>
+        <v>127727337</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2025,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539165</v>
+        <v>538658</v>
       </c>
       <c r="R14" t="n">
-        <v>7244399</v>
+        <v>7244502</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2097,6 +2092,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2105,26 +2105,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2141,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727378</v>
+        <v>127727374</v>
       </c>
       <c r="B15" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538857</v>
+        <v>538600</v>
       </c>
       <c r="R15" t="n">
-        <v>7244381</v>
+        <v>7244556</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,9 +2213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2253,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727357</v>
+        <v>127727375</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,39 +2249,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539013</v>
+        <v>539165</v>
       </c>
       <c r="R16" t="n">
-        <v>7244500</v>
+        <v>7244399</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2331,11 +2311,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,6 +2319,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2360,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727337</v>
+        <v>127727378</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,39 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538658</v>
+        <v>538857</v>
       </c>
       <c r="R17" t="n">
-        <v>7244502</v>
+        <v>7244381</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2438,11 +2428,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2451,6 +2436,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2805,7 +2805,7 @@
         <v>127727387</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727360</v>
+        <v>127727376</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,39 +2930,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538856</v>
+        <v>539109</v>
       </c>
       <c r="R22" t="n">
-        <v>7244394</v>
+        <v>7244501</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2997,11 +2992,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3010,6 +3000,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3026,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727376</v>
+        <v>127727360</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,34 +3047,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539109</v>
+        <v>538856</v>
       </c>
       <c r="R23" t="n">
-        <v>7244501</v>
+        <v>7244394</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,6 +3114,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3107,26 +3127,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727383</v>
+        <v>127727399</v>
       </c>
       <c r="B24" t="n">
-        <v>91366</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538911</v>
+        <v>538900</v>
       </c>
       <c r="R24" t="n">
-        <v>7244544</v>
+        <v>7244576</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3224,26 +3224,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3260,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727399</v>
+        <v>127727336</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,34 +3251,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538900</v>
+        <v>538852</v>
       </c>
       <c r="R25" t="n">
-        <v>7244576</v>
+        <v>7244404</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,6 +3316,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727336</v>
+        <v>127727383</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>91374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,39 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538852</v>
+        <v>538911</v>
       </c>
       <c r="R26" t="n">
-        <v>7244404</v>
+        <v>7244544</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3435,11 +3420,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3448,6 +3428,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727380</v>
+        <v>127727346</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,34 +3475,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538993</v>
+        <v>538953</v>
       </c>
       <c r="R27" t="n">
-        <v>7244440</v>
+        <v>7244425</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3542,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3545,21 +3555,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3576,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727395</v>
+        <v>127727353</v>
       </c>
       <c r="B28" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,34 +3582,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R28" t="n">
-        <v>7244472</v>
+        <v>7244570</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,6 +3649,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3657,26 +3662,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3693,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727353</v>
+        <v>127727395</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,39 +3689,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R29" t="n">
-        <v>7244570</v>
+        <v>7244472</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3771,11 +3751,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3784,6 +3759,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3800,10 +3795,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727346</v>
+        <v>127727380</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,39 +3806,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538953</v>
+        <v>538993</v>
       </c>
       <c r="R30" t="n">
-        <v>7244425</v>
+        <v>7244440</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3878,11 +3868,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3876,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727372</v>
+        <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91348</v>
+        <v>91720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538755</v>
+        <v>538633</v>
       </c>
       <c r="R31" t="n">
-        <v>7244423</v>
+        <v>7244525</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3991,22 +3991,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Granstubbe och låga</t>
+          <t>Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe och låga</t>
+          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,32 +4024,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727386</v>
+        <v>127727372</v>
       </c>
       <c r="B32" t="n">
-        <v>91712</v>
+        <v>91356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538633</v>
+        <v>538755</v>
       </c>
       <c r="R32" t="n">
-        <v>7244525</v>
+        <v>7244423</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
+          <t>Granstubbe och låga</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
+          <t>Picea abies # Granstubbe och låga</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
         <v>127727358</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>127727393</v>
       </c>
       <c r="B34" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R36" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R37" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727368</v>
+        <v>127727330</v>
       </c>
       <c r="B38" t="n">
-        <v>91721</v>
+        <v>91325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1506</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539047</v>
+        <v>538757</v>
       </c>
       <c r="R38" t="n">
-        <v>7244483</v>
+        <v>7244545</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4778,14 +4778,24 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Toppknäckt gran</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
+          <t>Picea abies # Toppknäckt gran</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4806,7 +4816,7 @@
         <v>127727384</v>
       </c>
       <c r="B39" t="n">
-        <v>91762</v>
+        <v>91770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4920,50 +4930,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727356</v>
+        <v>127727368</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>91729</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538874</v>
+        <v>539047</v>
       </c>
       <c r="R40" t="n">
-        <v>7244402</v>
+        <v>7244483</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4998,11 +5003,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5011,6 +5011,16 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5027,45 +5037,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727330</v>
+        <v>127727356</v>
       </c>
       <c r="B41" t="n">
-        <v>91317</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538757</v>
+        <v>538874</v>
       </c>
       <c r="R41" t="n">
-        <v>7244545</v>
+        <v>7244402</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,6 +5115,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5108,26 +5128,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5147,7 +5147,7 @@
         <v>127727361</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727398</v>
+        <v>127727349</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5369,34 +5369,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538623</v>
+        <v>539183</v>
       </c>
       <c r="R44" t="n">
-        <v>7244488</v>
+        <v>7244439</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,6 +5434,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5458,7 +5468,7 @@
         <v>127727343</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,10 +5572,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727349</v>
+        <v>127727398</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5573,39 +5583,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539183</v>
+        <v>538623</v>
       </c>
       <c r="R46" t="n">
-        <v>7244439</v>
+        <v>7244488</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5638,11 +5643,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5672,7 +5672,7 @@
         <v>127727400</v>
       </c>
       <c r="B47" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>127727338</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B49" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R49" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,10 +6000,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R50" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6135,10 +6135,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6147,10 +6151,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R51" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6183,11 +6187,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6214,10 +6213,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727371</v>
+        <v>127727339</v>
       </c>
       <c r="B52" t="n">
-        <v>56855</v>
+        <v>57673</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,16 +6224,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6242,14 +6241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539227</v>
+        <v>538694</v>
       </c>
       <c r="R52" t="n">
-        <v>7244447</v>
+        <v>7244432</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6294,6 +6289,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6320,10 +6320,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727379</v>
+        <v>127727396</v>
       </c>
       <c r="B53" t="n">
-        <v>91348</v>
+        <v>91378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6331,21 +6331,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>538959</v>
+        <v>539008</v>
       </c>
       <c r="R53" t="n">
-        <v>7244418</v>
+        <v>7244491</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6412,9 +6412,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6432,32 +6437,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727334</v>
+        <v>127727379</v>
       </c>
       <c r="B54" t="n">
-        <v>92049</v>
+        <v>91356</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6472,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539146</v>
+        <v>538959</v>
       </c>
       <c r="R54" t="n">
-        <v>7244417</v>
+        <v>7244418</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6544,10 +6549,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727355</v>
+        <v>127727348</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6575,7 +6580,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6584,10 +6589,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>538621</v>
+        <v>539079</v>
       </c>
       <c r="R55" t="n">
-        <v>7244491</v>
+        <v>7244407</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6624,7 +6629,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6651,10 +6656,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127727348</v>
+        <v>127727355</v>
       </c>
       <c r="B56" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6687,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539079</v>
+        <v>538621</v>
       </c>
       <c r="R56" t="n">
-        <v>7244407</v>
+        <v>7244491</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6731,7 +6736,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6758,32 +6763,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727396</v>
+        <v>127727334</v>
       </c>
       <c r="B57" t="n">
-        <v>91370</v>
+        <v>92057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6793,10 +6798,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539008</v>
+        <v>539146</v>
       </c>
       <c r="R57" t="n">
-        <v>7244491</v>
+        <v>7244417</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6850,14 +6855,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727357</v>
+        <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539013</v>
+        <v>538600</v>
       </c>
       <c r="R13" t="n">
-        <v>7244500</v>
+        <v>7244556</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,11 +1980,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,6 +1988,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Stående, död</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående, död</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2014,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727337</v>
+        <v>127727375</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,39 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538658</v>
+        <v>539165</v>
       </c>
       <c r="R14" t="n">
-        <v>7244502</v>
+        <v>7244399</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2092,11 +2097,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2105,6 +2105,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2121,7 +2141,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727374</v>
+        <v>127727378</v>
       </c>
       <c r="B15" t="n">
         <v>91356</v>
@@ -2156,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538600</v>
+        <v>538857</v>
       </c>
       <c r="R15" t="n">
-        <v>7244556</v>
+        <v>7244381</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2213,14 +2233,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Stående, död</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727375</v>
+        <v>127727357</v>
       </c>
       <c r="B16" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,34 +2264,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539165</v>
+        <v>539013</v>
       </c>
       <c r="R16" t="n">
-        <v>7244399</v>
+        <v>7244500</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2311,6 +2331,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2319,26 +2344,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2355,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727378</v>
+        <v>127727337</v>
       </c>
       <c r="B17" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,34 +2371,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538857</v>
+        <v>538658</v>
       </c>
       <c r="R17" t="n">
-        <v>7244381</v>
+        <v>7244502</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,6 +2438,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2436,21 +2451,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,39 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2540,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2595,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,6 +2662,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2655,26 +2675,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727346</v>
+        <v>127727395</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,39 +3475,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538953</v>
+        <v>538993</v>
       </c>
       <c r="R27" t="n">
-        <v>7244425</v>
+        <v>7244472</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3542,11 +3537,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3555,6 +3545,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3571,10 +3581,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727353</v>
+        <v>127727380</v>
       </c>
       <c r="B28" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,39 +3592,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538793</v>
+        <v>538993</v>
       </c>
       <c r="R28" t="n">
-        <v>7244570</v>
+        <v>7244440</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,11 +3654,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3662,6 +3662,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3678,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727395</v>
+        <v>127727346</v>
       </c>
       <c r="B29" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,34 +3704,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538993</v>
+        <v>538953</v>
       </c>
       <c r="R29" t="n">
-        <v>7244472</v>
+        <v>7244425</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3751,6 +3771,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3759,26 +3784,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3795,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727380</v>
+        <v>127727353</v>
       </c>
       <c r="B30" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,34 +3811,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538993</v>
+        <v>538793</v>
       </c>
       <c r="R30" t="n">
-        <v>7244440</v>
+        <v>7244570</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3868,6 +3878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3876,21 +3891,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4813,32 +4813,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727384</v>
+        <v>127727368</v>
       </c>
       <c r="B39" t="n">
-        <v>91770</v>
+        <v>91729</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539028</v>
+        <v>539047</v>
       </c>
       <c r="R39" t="n">
-        <v>7244444</v>
+        <v>7244483</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4895,24 +4895,14 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4930,45 +4920,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727368</v>
+        <v>127727356</v>
       </c>
       <c r="B40" t="n">
-        <v>91729</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539047</v>
+        <v>538874</v>
       </c>
       <c r="R40" t="n">
-        <v>7244483</v>
+        <v>7244402</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5003,6 +4998,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5011,16 +5011,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5037,50 +5027,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727356</v>
+        <v>127727384</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>91770</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>538874</v>
+        <v>539028</v>
       </c>
       <c r="R41" t="n">
-        <v>7244402</v>
+        <v>7244444</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5115,11 +5100,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5128,6 +5108,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>lutande grov granstam</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # lutande grov granstam</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727389</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127727333</v>
       </c>
       <c r="B3" t="n">
-        <v>92057</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>127727352</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>127727369</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>58054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>127727394</v>
       </c>
       <c r="B6" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127727377</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>127727385</v>
       </c>
       <c r="B8" t="n">
-        <v>91374</v>
+        <v>91385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,50 +1469,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727341</v>
+        <v>127727331</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>92068</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538761</v>
+        <v>539188</v>
       </c>
       <c r="R9" t="n">
-        <v>7244400</v>
+        <v>7244462</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,11 +1542,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1560,6 +1550,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1579,7 +1589,7 @@
         <v>127727351</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1696,7 @@
         <v>127727347</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,45 +1800,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727331</v>
+        <v>127727341</v>
       </c>
       <c r="B12" t="n">
-        <v>92057</v>
+        <v>57684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539188</v>
+        <v>538761</v>
       </c>
       <c r="R12" t="n">
-        <v>7244462</v>
+        <v>7244400</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,6 +1878,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1871,26 +1891,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1910,7 +1910,7 @@
         <v>127727374</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>127727375</v>
       </c>
       <c r="B14" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>127727378</v>
       </c>
       <c r="B15" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>127727357</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>127727337</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727373</v>
+        <v>127727354</v>
       </c>
       <c r="B18" t="n">
-        <v>91356</v>
+        <v>57684</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,34 +2478,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538704</v>
+        <v>538693</v>
       </c>
       <c r="R18" t="n">
-        <v>7244578</v>
+        <v>7244542</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,6 +2545,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2548,26 +2558,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2584,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727354</v>
+        <v>127727373</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>91367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,39 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538693</v>
+        <v>538704</v>
       </c>
       <c r="R19" t="n">
-        <v>7244542</v>
+        <v>7244578</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,11 +2647,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2675,6 +2655,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2694,7 +2694,7 @@
         <v>127727363</v>
       </c>
       <c r="B20" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727387</v>
+        <v>127727376</v>
       </c>
       <c r="B21" t="n">
-        <v>91378</v>
+        <v>91367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538961</v>
+        <v>539109</v>
       </c>
       <c r="R21" t="n">
-        <v>7244436</v>
+        <v>7244501</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727376</v>
+        <v>127727387</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539109</v>
+        <v>538961</v>
       </c>
       <c r="R22" t="n">
-        <v>7244501</v>
+        <v>7244436</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # låga, knäckt nyfallen</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
         <v>127727360</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727399</v>
+        <v>127727336</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>57684</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,34 +3154,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538900</v>
+        <v>538852</v>
       </c>
       <c r="R24" t="n">
-        <v>7244576</v>
+        <v>7244404</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3214,6 +3219,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727336</v>
+        <v>127727383</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>91385</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,39 +3261,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538852</v>
+        <v>538911</v>
       </c>
       <c r="R25" t="n">
-        <v>7244404</v>
+        <v>7244544</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3318,11 +3323,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3331,6 +3331,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3347,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727383</v>
+        <v>127727399</v>
       </c>
       <c r="B26" t="n">
-        <v>91374</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538911</v>
+        <v>538900</v>
       </c>
       <c r="R26" t="n">
-        <v>7244544</v>
+        <v>7244576</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3428,26 +3448,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727395</v>
+        <v>127727380</v>
       </c>
       <c r="B27" t="n">
-        <v>91378</v>
+        <v>91367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
         <v>538993</v>
       </c>
       <c r="R27" t="n">
-        <v>7244472</v>
+        <v>7244440</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3556,14 +3556,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3581,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727380</v>
+        <v>127727395</v>
       </c>
       <c r="B28" t="n">
-        <v>91356</v>
+        <v>91389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,21 +3587,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3619,7 +3614,7 @@
         <v>538993</v>
       </c>
       <c r="R28" t="n">
-        <v>7244440</v>
+        <v>7244472</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3673,9 +3668,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727346</v>
+        <v>127727353</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538953</v>
+        <v>538793</v>
       </c>
       <c r="R29" t="n">
-        <v>7244425</v>
+        <v>7244570</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727353</v>
+        <v>127727346</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538793</v>
+        <v>538953</v>
       </c>
       <c r="R30" t="n">
-        <v>7244570</v>
+        <v>7244425</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3910,7 +3910,7 @@
         <v>127727386</v>
       </c>
       <c r="B31" t="n">
-        <v>91720</v>
+        <v>91731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>127727372</v>
       </c>
       <c r="B32" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727358</v>
+        <v>127727393</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>91389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,39 +4152,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538729</v>
+        <v>538905</v>
       </c>
       <c r="R33" t="n">
-        <v>7244550</v>
+        <v>7244572</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4219,11 +4214,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack lågt</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4232,6 +4222,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4248,10 +4258,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727393</v>
+        <v>127727358</v>
       </c>
       <c r="B34" t="n">
-        <v>91378</v>
+        <v>57684</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,34 +4269,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538905</v>
+        <v>538729</v>
       </c>
       <c r="R34" t="n">
-        <v>7244572</v>
+        <v>7244550</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4321,6 +4336,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4329,26 +4349,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4368,7 +4368,7 @@
         <v>127727388</v>
       </c>
       <c r="B35" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727345</v>
+        <v>127727359</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538931</v>
+        <v>538744</v>
       </c>
       <c r="R36" t="n">
-        <v>7244442</v>
+        <v>7244385</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727359</v>
+        <v>127727345</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538744</v>
+        <v>538931</v>
       </c>
       <c r="R37" t="n">
-        <v>7244385</v>
+        <v>7244442</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4699,7 +4699,7 @@
         <v>127727330</v>
       </c>
       <c r="B38" t="n">
-        <v>91325</v>
+        <v>91336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>127727368</v>
       </c>
       <c r="B39" t="n">
-        <v>91729</v>
+        <v>91740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>127727356</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>127727384</v>
       </c>
       <c r="B41" t="n">
-        <v>91770</v>
+        <v>91781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>127727361</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>127727367</v>
       </c>
       <c r="B43" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727349</v>
+        <v>127727343</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539183</v>
+        <v>538886</v>
       </c>
       <c r="R44" t="n">
-        <v>7244439</v>
+        <v>7244392</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727343</v>
+        <v>127727349</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>538886</v>
+        <v>539183</v>
       </c>
       <c r="R45" t="n">
-        <v>7244392</v>
+        <v>7244439</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5575,7 +5575,7 @@
         <v>127727398</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727400</v>
+        <v>127727338</v>
       </c>
       <c r="B47" t="n">
-        <v>88761</v>
+        <v>57684</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5680,34 +5680,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538755</v>
+        <v>538714</v>
       </c>
       <c r="R47" t="n">
-        <v>7244393</v>
+        <v>7244425</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5742,6 +5747,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5760,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727338</v>
+        <v>127727400</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>88772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538714</v>
+        <v>538755</v>
       </c>
       <c r="R48" t="n">
-        <v>7244425</v>
+        <v>7244393</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5864,11 +5849,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5877,6 +5857,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5893,10 +5893,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727344</v>
+        <v>127727335</v>
       </c>
       <c r="B49" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538883</v>
+        <v>538997</v>
       </c>
       <c r="R49" t="n">
-        <v>7244412</v>
+        <v>7244459</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,10 +6000,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727335</v>
+        <v>127727344</v>
       </c>
       <c r="B50" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538997</v>
+        <v>538883</v>
       </c>
       <c r="R50" t="n">
-        <v>7244459</v>
+        <v>7244412</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,7 +6110,7 @@
         <v>127727371</v>
       </c>
       <c r="B51" t="n">
-        <v>56855</v>
+        <v>56866</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>127727339</v>
       </c>
       <c r="B52" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727396</v>
+        <v>127727379</v>
       </c>
       <c r="B53" t="n">
-        <v>91378</v>
+        <v>91367</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6331,21 +6331,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539008</v>
+        <v>538959</v>
       </c>
       <c r="R53" t="n">
-        <v>7244491</v>
+        <v>7244418</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6412,14 +6412,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6437,10 +6432,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127727379</v>
+        <v>127727396</v>
       </c>
       <c r="B54" t="n">
-        <v>91356</v>
+        <v>91389</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6448,21 +6443,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6472,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538959</v>
+        <v>539008</v>
       </c>
       <c r="R54" t="n">
-        <v>7244418</v>
+        <v>7244491</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6529,9 +6524,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Knäckt</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6549,50 +6549,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127727348</v>
+        <v>127727334</v>
       </c>
       <c r="B55" t="n">
-        <v>57673</v>
+        <v>92068</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539079</v>
+        <v>539146</v>
       </c>
       <c r="R55" t="n">
-        <v>7244407</v>
+        <v>7244417</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6627,11 +6622,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6640,6 +6630,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6659,7 +6664,7 @@
         <v>127727355</v>
       </c>
       <c r="B56" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6763,45 +6768,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127727334</v>
+        <v>127727348</v>
       </c>
       <c r="B57" t="n">
-        <v>92057</v>
+        <v>57684</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539146</v>
+        <v>539079</v>
       </c>
       <c r="R57" t="n">
-        <v>7244417</v>
+        <v>7244407</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6836,6 +6846,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6844,21 +6859,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6873,6 +6873,253 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127727366</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91922</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>S Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>539120</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7244484</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Kollekt för mikroskopering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127727329</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91922</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>S Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>539150</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7244494</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Kollekt för mikroskopering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>granrot vid ån</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # granrot vid ån</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91923</v>
+        <v>91926</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91923</v>
+        <v>91926</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91926</v>
+        <v>91954</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91926</v>
+        <v>91954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91954</v>
+        <v>91960</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91954</v>
+        <v>91960</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91960</v>
+        <v>91961</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91960</v>
+        <v>91961</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91961</v>
+        <v>91966</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91961</v>
+        <v>91966</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -6878,7 +6878,7 @@
         <v>127727366</v>
       </c>
       <c r="B58" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>127727329</v>
       </c>
       <c r="B59" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18848-2025 artfynd.xlsx
+++ b/artfynd/A 18848-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727389</v>
+        <v>127727400</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538633</v>
+        <v>538755</v>
       </c>
       <c r="R2" t="n">
-        <v>7244525</v>
+        <v>7244393</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granhögstubbe och låga knäckt med GTP</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe och låga knäckt med GTP</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727333</v>
+        <v>127727367</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539048</v>
+        <v>539047</v>
       </c>
       <c r="R3" t="n">
-        <v>7244482</v>
+        <v>7244483</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,24 +874,14 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>stående 2stammig lutar</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # stående 2stammig lutar</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727352</v>
+        <v>127727372</v>
       </c>
       <c r="B4" t="n">
-        <v>57684</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539002</v>
+        <v>538755</v>
       </c>
       <c r="R4" t="n">
-        <v>7244475</v>
+        <v>7244423</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +972,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,6 +980,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granstubbe och låga</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe och låga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,50 +1016,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727369</v>
+        <v>127727373</v>
       </c>
       <c r="B5" t="n">
-        <v>58054</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538906</v>
+        <v>538704</v>
       </c>
       <c r="R5" t="n">
-        <v>7244545</v>
+        <v>7244578</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,6 +1097,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727394</v>
+        <v>127727374</v>
       </c>
       <c r="B6" t="n">
-        <v>91389</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539095</v>
+        <v>538600</v>
       </c>
       <c r="R6" t="n">
-        <v>7244407</v>
+        <v>7244556</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,12 +1227,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Stående, död</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Stående, död</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727377</v>
+        <v>127727375</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539032</v>
+        <v>539165</v>
       </c>
       <c r="R7" t="n">
-        <v>7244470</v>
+        <v>7244399</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,12 +1344,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Ny rotvälta</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Ny rotvälta</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727385</v>
+        <v>127727376</v>
       </c>
       <c r="B8" t="n">
-        <v>91385</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539028</v>
+        <v>539109</v>
       </c>
       <c r="R8" t="n">
-        <v>7244444</v>
+        <v>7244501</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,12 +1461,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>lutande grov granstam</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # lutande grov granstam</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,32 +1484,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727331</v>
+        <v>127727377</v>
       </c>
       <c r="B9" t="n">
-        <v>92068</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539188</v>
+        <v>539032</v>
       </c>
       <c r="R9" t="n">
-        <v>7244462</v>
+        <v>7244470</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,12 +1578,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Ny rotvälta</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Ny rotvälta</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1586,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727351</v>
+        <v>127727378</v>
       </c>
       <c r="B10" t="n">
-        <v>57684</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539184</v>
+        <v>538857</v>
       </c>
       <c r="R10" t="n">
-        <v>7244459</v>
+        <v>7244381</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,11 +1674,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1677,6 +1682,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1693,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727347</v>
+        <v>127727379</v>
       </c>
       <c r="B11" t="n">
-        <v>57684</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,39 +1724,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539057</v>
+        <v>538959</v>
       </c>
       <c r="R11" t="n">
-        <v>7244431</v>
+        <v>7244418</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,11 +1786,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1784,6 +1794,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1800,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727341</v>
+        <v>127727380</v>
       </c>
       <c r="B12" t="n">
-        <v>57684</v>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1836,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538761</v>
+        <v>538993</v>
       </c>
       <c r="R12" t="n">
-        <v>7244400</v>
+        <v>7244440</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1878,11 +1898,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,6 +1906,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1907,32 +1937,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727374</v>
+        <v>127727383</v>
       </c>
       <c r="B13" t="n">
-        <v>91367</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538600</v>
+        <v>538911</v>
       </c>
       <c r="R13" t="n">
-        <v>7244556</v>
+        <v>7244544</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2001,12 +2031,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Stående, död</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, död</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2024,32 +2054,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727375</v>
+        <v>127727385</v>
       </c>
       <c r="B14" t="n">
-        <v>91367</v>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539165</v>
+        <v>539028</v>
       </c>
       <c r="R14" t="n">
-        <v>7244399</v>
+        <v>7244444</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,12 +2148,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Stående</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2141,32 +2171,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727378</v>
+        <v>127727368</v>
       </c>
       <c r="B15" t="n">
-        <v>91367</v>
+        <v>92292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538857</v>
+        <v>539047</v>
       </c>
       <c r="R15" t="n">
-        <v>7244381</v>
+        <v>7244483</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2223,19 +2253,14 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Granlåga mossbevuxen rotvälta</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2253,50 +2278,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727357</v>
+        <v>127727329</v>
       </c>
       <c r="B16" t="n">
-        <v>57684</v>
+        <v>92283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539013</v>
+        <v>539150</v>
       </c>
       <c r="R16" t="n">
-        <v>7244500</v>
+        <v>7244494</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,7 +2356,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på 2 olika granar</t>
+          <t>Kollekt för mikroskopering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,8 +2365,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>granrot vid ån</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # granrot vid ån</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2360,50 +2404,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727337</v>
+        <v>127727366</v>
       </c>
       <c r="B17" t="n">
-        <v>57684</v>
+        <v>92283</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538658</v>
+        <v>539120</v>
       </c>
       <c r="R17" t="n">
-        <v>7244502</v>
+        <v>7244484</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2440,7 +2482,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Kollekt för mikroskopering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,8 +2491,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2467,50 +2525,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727354</v>
+        <v>127727386</v>
       </c>
       <c r="B18" t="n">
-        <v>57684</v>
+        <v>92283</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538693</v>
+        <v>538633</v>
       </c>
       <c r="R18" t="n">
-        <v>7244542</v>
+        <v>7244525</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,11 +2598,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2558,6 +2606,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Grantickeporing på minst 4 grantickor</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat. # Grantickeporing på minst 4 grantickor</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,32 +2642,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727373</v>
+        <v>127727331</v>
       </c>
       <c r="B19" t="n">
-        <v>91367</v>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2609,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538704</v>
+        <v>539188</v>
       </c>
       <c r="R19" t="n">
-        <v>7244578</v>
+        <v>7244462</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2668,12 +2736,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2691,10 +2759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727363</v>
+        <v>127727333</v>
       </c>
       <c r="B20" t="n">
-        <v>56875</v>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,48 +2770,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538617</v>
+        <v>539048</v>
       </c>
       <c r="R20" t="n">
-        <v>7244542</v>
+        <v>7244482</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2786,6 +2840,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>stående 2stammig lutar</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # stående 2stammig lutar</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2802,32 +2876,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727376</v>
+        <v>127727334</v>
       </c>
       <c r="B21" t="n">
-        <v>91367</v>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539109</v>
+        <v>539146</v>
       </c>
       <c r="R21" t="n">
-        <v>7244501</v>
+        <v>7244417</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2894,14 +2968,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,32 +2988,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727387</v>
+        <v>127727384</v>
       </c>
       <c r="B22" t="n">
-        <v>91389</v>
+        <v>92333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2954,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538961</v>
+        <v>539028</v>
       </c>
       <c r="R22" t="n">
-        <v>7244436</v>
+        <v>7244444</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3013,12 +3082,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>låga, knäckt nyfallen</t>
+          <t>lutande grov granstam</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # låga, knäckt nyfallen</t>
+          <t>Picea abies # lutande grov granstam</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3036,50 +3105,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727360</v>
+        <v>127727330</v>
       </c>
       <c r="B23" t="n">
-        <v>57684</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538856</v>
+        <v>538757</v>
       </c>
       <c r="R23" t="n">
-        <v>7244394</v>
+        <v>7244545</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3114,11 +3178,6 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3127,6 +3186,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Toppknäckt gran</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Toppknäckt gran</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3143,50 +3222,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727336</v>
+        <v>127727398</v>
       </c>
       <c r="B24" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538852</v>
+        <v>538623</v>
       </c>
       <c r="R24" t="n">
-        <v>7244404</v>
+        <v>7244488</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3219,11 +3293,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack och barkfläng</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,32 +3319,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127727383</v>
+        <v>127727399</v>
       </c>
       <c r="B25" t="n">
-        <v>91385</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3354,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538911</v>
+        <v>538900</v>
       </c>
       <c r="R25" t="n">
-        <v>7244544</v>
+        <v>7244576</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,26 +3400,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3367,10 +3416,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127727399</v>
+        <v>127727335</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,34 +3427,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538900</v>
+        <v>538997</v>
       </c>
       <c r="R26" t="n">
-        <v>7244576</v>
+        <v>7244459</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3438,6 +3492,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng 2-stammig gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127727380</v>
+        <v>127727336</v>
       </c>
       <c r="B27" t="n">
-        <v>91367</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,34 +3534,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538993</v>
+        <v>538852</v>
       </c>
       <c r="R27" t="n">
-        <v>7244440</v>
+        <v>7244404</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,6 +3601,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläng</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3545,21 +3614,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3576,10 +3630,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127727395</v>
+        <v>127727337</v>
       </c>
       <c r="B28" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,34 +3641,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538993</v>
+        <v>538658</v>
       </c>
       <c r="R28" t="n">
-        <v>7244472</v>
+        <v>7244502</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,6 +3708,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3657,26 +3721,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3693,10 +3737,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127727353</v>
+        <v>127727338</v>
       </c>
       <c r="B29" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,10 +3777,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538793</v>
+        <v>538714</v>
       </c>
       <c r="R29" t="n">
-        <v>7244570</v>
+        <v>7244425</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3800,10 +3844,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127727346</v>
+        <v>127727339</v>
       </c>
       <c r="B30" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3840,10 +3884,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>538953</v>
+        <v>538694</v>
       </c>
       <c r="R30" t="n">
-        <v>7244425</v>
+        <v>7244432</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3907,45 +3951,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127727386</v>
+        <v>127727341</v>
       </c>
       <c r="B31" t="n">
-        <v>91731</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538633</v>
+        <v>538761</v>
       </c>
       <c r="R31" t="n">
-        <v>7244525</v>
+        <v>7244400</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3980,6 +4029,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3988,26 +4042,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Grantickeporing på minst 4 grantickor</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma # Grantickeporing på minst 4 grantickor</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4024,10 +4058,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127727372</v>
+        <v>127727343</v>
       </c>
       <c r="B32" t="n">
-        <v>91367</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,34 +4069,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>538755</v>
+        <v>538886</v>
       </c>
       <c r="R32" t="n">
-        <v>7244423</v>
+        <v>7244392</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4097,6 +4136,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4105,26 +4149,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Granstubbe och låga</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe och låga</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4141,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127727393</v>
+        <v>127727344</v>
       </c>
       <c r="B33" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,34 +4176,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538905</v>
+        <v>538883</v>
       </c>
       <c r="R33" t="n">
-        <v>7244572</v>
+        <v>7244412</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4214,6 +4243,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4222,26 +4256,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4258,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127727358</v>
+        <v>127727345</v>
       </c>
       <c r="B34" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,7 +4303,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4298,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538729</v>
+        <v>538931</v>
       </c>
       <c r="R34" t="n">
-        <v>7244550</v>
+        <v>7244442</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4338,7 +4352,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack lågt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4365,10 +4379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127727388</v>
+        <v>127727346</v>
       </c>
       <c r="B35" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,34 +4390,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>538854</v>
+        <v>538953</v>
       </c>
       <c r="R35" t="n">
-        <v>7244608</v>
+        <v>7244425</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4438,6 +4457,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4446,26 +4470,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Granlåga invid ån</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga invid ån</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4482,10 +4486,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127727359</v>
+        <v>127727347</v>
       </c>
       <c r="B36" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4513,7 +4517,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4522,10 +4526,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538744</v>
+        <v>539057</v>
       </c>
       <c r="R36" t="n">
-        <v>7244385</v>
+        <v>7244431</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4589,10 +4593,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127727345</v>
+        <v>127727348</v>
       </c>
       <c r="B37" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4629,10 +4633,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538931</v>
+        <v>539079</v>
       </c>
       <c r="R37" t="n">
-        <v>7244442</v>
+        <v>7244407</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4696,45 +4700,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127727330</v>
+        <v>127727349</v>
       </c>
       <c r="B38" t="n">
-        <v>91336</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>538757</v>
+        <v>539183</v>
       </c>
       <c r="R38" t="n">
-        <v>7244545</v>
+        <v>7244439</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4769,6 +4778,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4777,26 +4791,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Toppknäckt gran</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies # Toppknäckt gran</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4813,45 +4807,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127727368</v>
+        <v>127727351</v>
       </c>
       <c r="B39" t="n">
-        <v>91740</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539047</v>
+        <v>539184</v>
       </c>
       <c r="R39" t="n">
-        <v>7244483</v>
+        <v>7244459</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4886,6 +4885,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4894,16 +4898,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4920,10 +4914,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127727356</v>
+        <v>127727352</v>
       </c>
       <c r="B40" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4951,7 +4945,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4960,10 +4954,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538874</v>
+        <v>539002</v>
       </c>
       <c r="R40" t="n">
-        <v>7244402</v>
+        <v>7244475</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5000,7 +4994,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5027,45 +5021,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127727384</v>
+        <v>127727353</v>
       </c>
       <c r="B41" t="n">
-        <v>91781</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539028</v>
+        <v>538793</v>
       </c>
       <c r="R41" t="n">
-        <v>7244444</v>
+        <v>7244570</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,6 +5099,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5108,26 +5112,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>lutande grov granstam</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # lutande grov granstam</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5144,10 +5128,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127727361</v>
+        <v>127727354</v>
       </c>
       <c r="B42" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5175,7 +5159,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5184,10 +5168,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539034</v>
+        <v>538693</v>
       </c>
       <c r="R42" t="n">
-        <v>7244443</v>
+        <v>7244542</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5251,10 +5235,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127727367</v>
+        <v>127727355</v>
       </c>
       <c r="B43" t="n">
-        <v>91667</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,34 +5246,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539047</v>
+        <v>538621</v>
       </c>
       <c r="R43" t="n">
-        <v>7244483</v>
+        <v>7244491</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,6 +5313,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, rikligt</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5332,16 +5326,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen rotvälta</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5358,10 +5342,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127727343</v>
+        <v>127727356</v>
       </c>
       <c r="B44" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5389,7 +5373,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5398,10 +5382,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>538886</v>
+        <v>538874</v>
       </c>
       <c r="R44" t="n">
-        <v>7244392</v>
+        <v>7244402</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5438,7 +5422,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5465,10 +5449,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127727349</v>
+        <v>127727357</v>
       </c>
       <c r="B45" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5496,7 +5480,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5505,10 +5489,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539183</v>
+        <v>539013</v>
       </c>
       <c r="R45" t="n">
-        <v>7244439</v>
+        <v>7244500</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5545,7 +5529,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, färska och äldre på 2 olika granar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5572,10 +5556,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127727398</v>
+        <v>127727358</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5583,34 +5567,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>538623</v>
+        <v>538729</v>
       </c>
       <c r="R46" t="n">
-        <v>7244488</v>
+        <v>7244550</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5643,6 +5632,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack lågt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5669,10 +5663,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127727338</v>
+        <v>127727359</v>
       </c>
       <c r="B47" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5700,7 +5694,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5709,10 +5703,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>538714</v>
+        <v>538744</v>
       </c>
       <c r="R47" t="n">
-        <v>7244425</v>
+        <v>7244385</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5776,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127727400</v>
+        <v>127727360</v>
       </c>
       <c r="B48" t="n">
-        <v>88772</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,34 +5781,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538755</v>
+        <v>538856</v>
       </c>
       <c r="R48" t="n">
-        <v>7244393</v>
+        <v>7244394</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,6 +5848,11 @@
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5857,26 +5861,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5893,10 +5877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127727335</v>
+        <v>127727361</v>
       </c>
       <c r="B49" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,7 +5908,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5933,10 +5917,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>538997</v>
+        <v>539034</v>
       </c>
       <c r="R49" t="n">
-        <v>7244459</v>
+        <v>7244443</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5973,7 +5957,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläng 2-stammig gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,10 +5984,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127727344</v>
+        <v>127727362</v>
       </c>
       <c r="B50" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6031,7 +6015,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6040,10 +6024,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>538883</v>
+        <v>539263</v>
       </c>
       <c r="R50" t="n">
-        <v>7244412</v>
+        <v>7244456</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6107,37 +6091,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127727371</v>
+        <v>127727363</v>
       </c>
       <c r="B51" t="n">
-        <v>56866</v>
+        <v>57141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6151,10 +6140,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539227</v>
+        <v>538617</v>
       </c>
       <c r="R51" t="n">
-        <v>7244447</v>
+        <v>7244542</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6213,27 +6202,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127727339</v>
+        <v>127727371</v>
       </c>
       <c r="B52" t="n">
-        <v>57684</v>
+        <v>57132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6241,10 +6230,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6253,10 +6246,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>538694</v>
+        <v>539227</v>
       </c>
       <c r="R52" t="n">
-        <v>7244432</v>
+        <v>7244447</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6289,11 +6282,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6320,45 +6308,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127727379</v>
+        <v>127727369</v>
       </c>
       <c r="B53" t="n">
-        <v>91367</v>
+        <v>58327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>S Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>538959</v>
+        <v>538906</v>
       </c>
       <c r="R53" t="n">
-        <v>7244418</v>
+        <v>7244545</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6402,21 +6395,6 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
@@ -6429,696 +6407,6 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>127727396</v>
-      </c>
-      <c r="B54" t="n">
-        <v>91389</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>539008</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7244491</v>
-      </c>
-      <c r="S54" t="n">
-        <v>5</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Knäckt</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies # Knäckt</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>127727334</v>
-      </c>
-      <c r="B55" t="n">
-        <v>92068</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>539146</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7244417</v>
-      </c>
-      <c r="S55" t="n">
-        <v>5</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>127727355</v>
-      </c>
-      <c r="B56" t="n">
-        <v>57684</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>538621</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7244491</v>
-      </c>
-      <c r="S56" t="n">
-        <v>5</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, rikligt</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>127727348</v>
-      </c>
-      <c r="B57" t="n">
-        <v>57684</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>539079</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7244407</v>
-      </c>
-      <c r="S57" t="n">
-        <v>5</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>127727366</v>
-      </c>
-      <c r="B58" t="n">
-        <v>91972</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>2063</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Grantickeporing</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Skeletocutis chrysella</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>539120</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7244484</v>
-      </c>
-      <c r="S58" t="n">
-        <v>5</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kollekt för mikroskopering</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>127727329</v>
-      </c>
-      <c r="B59" t="n">
-        <v>91972</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>2063</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Grantickeporing</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Skeletocutis chrysella</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>S Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>539150</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7244494</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Kollekt för mikroskopering</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>granrot vid ån</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies # granrot vid ån</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
